--- a/Scripts/Prices regionalization.xlsx
+++ b/Scripts/Prices regionalization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Fossil vs. green chemicals\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6738AC1D-DBF8-434C-9A0C-775775C9AA5B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562D5297-5F84-427C-B858-9769622F51DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wind LCOH countries" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="86">
   <si>
     <t>Country</t>
   </si>
@@ -287,6 +287,15 @@
   <si>
     <t>Both inflation and natural gas</t>
   </si>
+  <si>
+    <t>PPP</t>
+  </si>
+  <si>
+    <t>Exchange rates</t>
+  </si>
+  <si>
+    <t>PPP in LCU</t>
+  </si>
 </sst>
 </file>
 
@@ -365,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -458,6 +467,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -561,7 +573,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -913,7 +925,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1589179247"/>
@@ -1012,7 +1024,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1046,7 +1058,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1643752831"/>
@@ -1088,7 +1100,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1118,7 +1130,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1194,7 +1206,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1546,7 +1558,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1589179247"/>
@@ -1645,7 +1657,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1679,7 +1691,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1643752831"/>
@@ -1721,7 +1733,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1746,7 +1758,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3262,21 +3274,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B1" s="34">
+      <c r="B1" s="35">
         <v>2019</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35">
         <v>2020</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35">
         <v>2021</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
       <c r="K1" s="2">
         <v>2022</v>
       </c>
@@ -11940,15 +11952,16 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D099D41-EC54-4A9B-8F6F-871BB4D178AD}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>78</v>
       </c>
@@ -11982,8 +11995,11 @@
       <c r="K1" s="19" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>2019</v>
       </c>
@@ -12019,7 +12035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>2020</v>
       </c>
@@ -12054,7 +12070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>2021</v>
       </c>
@@ -12089,7 +12105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>2022</v>
       </c>
@@ -12124,7 +12140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>78</v>
       </c>
@@ -12158,8 +12174,11 @@
       <c r="K7" s="19" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="19">
         <v>2019</v>
       </c>
@@ -12194,7 +12213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
         <v>2020</v>
       </c>
@@ -12229,7 +12248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="19">
         <v>2021</v>
       </c>
@@ -12264,7 +12283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
         <v>2022</v>
       </c>
@@ -12299,7 +12318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -12312,7 +12331,7 @@
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>79</v>
       </c>
@@ -12346,8 +12365,11 @@
       <c r="K13" s="19" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
         <v>2019</v>
       </c>
@@ -12392,7 +12414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
         <v>2020</v>
       </c>
@@ -12437,7 +12459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>2021</v>
       </c>
@@ -12545,21 +12567,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="B1" s="34">
+      <c r="B1" s="35">
         <v>2019</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35">
         <v>2020</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35">
         <v>2021</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
       <c r="K1" s="10">
         <v>2022</v>
       </c>
@@ -13219,7 +13241,7 @@
       <c r="I2" s="26">
         <v>6.0595152292610779</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="39" t="s">
         <v>80</v>
       </c>
     </row>
@@ -13251,7 +13273,7 @@
       <c r="I3" s="26">
         <v>6.073570022608787</v>
       </c>
-      <c r="J3" s="38"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
@@ -13281,7 +13303,7 @@
       <c r="I4" s="26">
         <v>6.0840794626795969</v>
       </c>
-      <c r="J4" s="38"/>
+      <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
@@ -13311,7 +13333,7 @@
       <c r="I5" s="26">
         <v>6.113455246973909</v>
       </c>
-      <c r="J5" s="38"/>
+      <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
@@ -13341,7 +13363,7 @@
       <c r="I6" s="26">
         <v>6.1535683869068301</v>
       </c>
-      <c r="J6" s="38"/>
+      <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
@@ -13371,7 +13393,7 @@
       <c r="I7" s="26">
         <v>6.1822097765937842</v>
       </c>
-      <c r="J7" s="38"/>
+      <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
@@ -13401,7 +13423,7 @@
       <c r="I8" s="26">
         <v>6.1996290378471226</v>
       </c>
-      <c r="J8" s="38"/>
+      <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
@@ -13431,7 +13453,7 @@
       <c r="I9" s="26">
         <v>6.2076603483315287</v>
       </c>
-      <c r="J9" s="38"/>
+      <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
@@ -13461,7 +13483,7 @@
       <c r="I10" s="26">
         <v>6.2112057016084279</v>
       </c>
-      <c r="J10" s="38"/>
+      <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
@@ -13491,7 +13513,7 @@
       <c r="I11" s="26">
         <v>6.2101674195773358</v>
       </c>
-      <c r="J11" s="38"/>
+      <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
@@ -13521,7 +13543,7 @@
       <c r="I12" s="24">
         <v>6.2082128709201356</v>
       </c>
-      <c r="J12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
@@ -13551,7 +13573,7 @@
       <c r="I13" s="28">
         <v>5.4740716409665193</v>
       </c>
-      <c r="J13" s="40" t="s">
+      <c r="J13" s="41" t="s">
         <v>81</v>
       </c>
     </row>
@@ -13583,7 +13605,7 @@
       <c r="I14" s="26">
         <v>5.4744347252575922</v>
       </c>
-      <c r="J14" s="38"/>
+      <c r="J14" s="39"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
@@ -13613,7 +13635,7 @@
       <c r="I15" s="26">
         <v>5.5433753550250042</v>
       </c>
-      <c r="J15" s="38"/>
+      <c r="J15" s="39"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
@@ -13643,7 +13665,7 @@
       <c r="I16" s="26">
         <v>5.4924981687384546</v>
       </c>
-      <c r="J16" s="38"/>
+      <c r="J16" s="39"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
@@ -13673,7 +13695,7 @@
       <c r="I17" s="26">
         <v>5.4707584968104817</v>
       </c>
-      <c r="J17" s="38"/>
+      <c r="J17" s="39"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
@@ -13703,7 +13725,7 @@
       <c r="I18" s="26">
         <v>5.4843741577257044</v>
       </c>
-      <c r="J18" s="38"/>
+      <c r="J18" s="39"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
@@ -13733,7 +13755,7 @@
       <c r="I19" s="26">
         <v>5.5549940523393273</v>
       </c>
-      <c r="J19" s="38"/>
+      <c r="J19" s="39"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
@@ -13763,7 +13785,7 @@
       <c r="I20" s="26">
         <v>5.6266578142897838</v>
       </c>
-      <c r="J20" s="38"/>
+      <c r="J20" s="39"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
@@ -13793,7 +13815,7 @@
       <c r="I21" s="26">
         <v>5.5433753550250042</v>
       </c>
-      <c r="J21" s="38"/>
+      <c r="J21" s="39"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
@@ -13823,7 +13845,7 @@
       <c r="I22" s="26">
         <v>5.4149796725944519</v>
       </c>
-      <c r="J22" s="38"/>
+      <c r="J22" s="39"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
@@ -13853,7 +13875,7 @@
       <c r="I23" s="24">
         <v>5.415569684567445</v>
       </c>
-      <c r="J23" s="39"/>
+      <c r="J23" s="40"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
@@ -13883,7 +13905,7 @@
       <c r="I24" s="28">
         <v>6.150603795651552</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="36" t="s">
         <v>82</v>
       </c>
     </row>
@@ -13915,7 +13937,7 @@
       <c r="I25" s="26">
         <v>6.1655861719250762</v>
       </c>
-      <c r="J25" s="36"/>
+      <c r="J25" s="37"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
@@ -13945,7 +13967,7 @@
       <c r="I26" s="26">
         <v>6.2449994696495681</v>
       </c>
-      <c r="J26" s="36"/>
+      <c r="J26" s="37"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
@@ -13975,7 +13997,7 @@
       <c r="I27" s="26">
         <v>6.2227138423414967</v>
       </c>
-      <c r="J27" s="36"/>
+      <c r="J27" s="37"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
@@ -14005,7 +14027,7 @@
       <c r="I28" s="26">
         <v>6.2396947384975237</v>
       </c>
-      <c r="J28" s="36"/>
+      <c r="J28" s="37"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
@@ -14035,7 +14057,7 @@
       <c r="I29" s="26">
         <v>6.2807941809932109</v>
       </c>
-      <c r="J29" s="36"/>
+      <c r="J29" s="37"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
@@ -14065,7 +14087,7 @@
       <c r="I30" s="26">
         <v>6.3671513082216116</v>
       </c>
-      <c r="J30" s="36"/>
+      <c r="J30" s="37"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
@@ -14095,7 +14117,7 @@
       <c r="I31" s="26">
         <v>6.4447194345643872</v>
       </c>
-      <c r="J31" s="36"/>
+      <c r="J31" s="37"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
@@ -14125,7 +14147,7 @@
       <c r="I32" s="26">
         <v>6.3597316472391725</v>
       </c>
-      <c r="J32" s="36"/>
+      <c r="J32" s="37"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
@@ -14155,7 +14177,7 @@
       <c r="I33" s="26">
         <v>6.2245584712274056</v>
       </c>
-      <c r="J33" s="36"/>
+      <c r="J33" s="37"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
@@ -14185,7 +14207,7 @@
       <c r="I34" s="24">
         <v>6.2256455918116629</v>
       </c>
-      <c r="J34" s="37"/>
+      <c r="J34" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14265,7 +14287,7 @@
       <c r="H2" s="26">
         <v>9.2513300410706787</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="39" t="s">
         <v>80</v>
       </c>
       <c r="J2" s="22"/>
@@ -14301,7 +14323,7 @@
       <c r="H3" s="26">
         <v>9.2727881160154872</v>
       </c>
-      <c r="I3" s="38"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
@@ -14328,7 +14350,7 @@
       <c r="H4" s="26">
         <v>9.2888333432264734</v>
       </c>
-      <c r="I4" s="38"/>
+      <c r="I4" s="39"/>
       <c r="Y4" s="22"/>
       <c r="Z4" s="22"/>
       <c r="AA4" s="22"/>
@@ -14364,7 +14386,7 @@
       <c r="H5" s="26">
         <v>9.3336826530210324</v>
       </c>
-      <c r="I5" s="38"/>
+      <c r="I5" s="39"/>
       <c r="Y5" s="22"/>
       <c r="Z5" s="22"/>
       <c r="AA5" s="22"/>
@@ -14400,7 +14422,7 @@
       <c r="H6" s="26">
         <v>9.3949251588094622</v>
       </c>
-      <c r="I6" s="38"/>
+      <c r="I6" s="39"/>
       <c r="Y6" s="22"/>
       <c r="Z6" s="22"/>
       <c r="AA6" s="22"/>
@@ -14436,7 +14458,7 @@
       <c r="H7" s="26">
         <v>9.4386532358591584</v>
       </c>
-      <c r="I7" s="38"/>
+      <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
@@ -14463,7 +14485,7 @@
       <c r="H8" s="26">
         <v>9.4652479928370887</v>
       </c>
-      <c r="I8" s="38"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
@@ -14490,7 +14512,7 @@
       <c r="H9" s="26">
         <v>9.4775097499484104</v>
       </c>
-      <c r="I9" s="38"/>
+      <c r="I9" s="39"/>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
@@ -14517,7 +14539,7 @@
       <c r="H10" s="26">
         <v>9.4829225976822347</v>
       </c>
-      <c r="I10" s="38"/>
+      <c r="I10" s="39"/>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
@@ -14544,7 +14566,7 @@
       <c r="H11" s="26">
         <v>9.4813374065601863</v>
       </c>
-      <c r="I11" s="38"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
@@ -14571,7 +14593,7 @@
       <c r="H12" s="24">
         <v>9.4783533106341995</v>
       </c>
-      <c r="I12" s="39"/>
+      <c r="I12" s="40"/>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
@@ -14598,7 +14620,7 @@
       <c r="H13" s="28">
         <v>8.3206843569337785</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="41" t="s">
         <v>81</v>
       </c>
       <c r="J13" s="22"/>
@@ -14634,7 +14656,7 @@
       <c r="H14" s="26">
         <v>8.3210983486660606</v>
       </c>
-      <c r="I14" s="38"/>
+      <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
@@ -14661,7 +14683,7 @@
       <c r="H15" s="26">
         <v>8.3997050288332584</v>
       </c>
-      <c r="I15" s="38"/>
+      <c r="I15" s="39"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
@@ -14688,7 +14710,7 @@
       <c r="H16" s="26">
         <v>8.3416944373471313</v>
       </c>
-      <c r="I16" s="38"/>
+      <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
@@ -14715,7 +14737,7 @@
       <c r="H17" s="26">
         <v>8.3169066823766986</v>
       </c>
-      <c r="I17" s="38"/>
+      <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
@@ -14742,7 +14764,7 @@
       <c r="H18" s="26">
         <v>8.3324313723373038</v>
       </c>
-      <c r="I18" s="38"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
@@ -14769,7 +14791,7 @@
       <c r="H19" s="26">
         <v>8.4129527642663078</v>
       </c>
-      <c r="I19" s="38"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
@@ -14796,7 +14818,7 @@
       <c r="H20" s="26">
         <v>8.4946643824256256</v>
       </c>
-      <c r="I20" s="38"/>
+      <c r="I20" s="39"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
@@ -14823,7 +14845,7 @@
       <c r="H21" s="26">
         <v>8.3997050288332584</v>
       </c>
-      <c r="I21" s="38"/>
+      <c r="I21" s="39"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
@@ -14850,7 +14872,7 @@
       <c r="H22" s="26">
         <v>8.253307202504752</v>
       </c>
-      <c r="I22" s="38"/>
+      <c r="I22" s="39"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
@@ -14877,7 +14899,7 @@
       <c r="H23" s="24">
         <v>8.2539799390697119</v>
       </c>
-      <c r="I23" s="39"/>
+      <c r="I23" s="40"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
@@ -14904,7 +14926,7 @@
       <c r="H24" s="28">
         <v>9.3551899830134921</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="36" t="s">
         <v>82</v>
       </c>
       <c r="J24" s="22"/>
@@ -14940,7 +14962,7 @@
       <c r="H25" s="26">
         <v>9.3777056957348073</v>
       </c>
-      <c r="I25" s="36"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
@@ -14967,7 +14989,7 @@
       <c r="H26" s="26">
         <v>9.4723156752426938</v>
       </c>
-      <c r="I26" s="36"/>
+      <c r="I26" s="37"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
@@ -14994,7 +15016,7 @@
       <c r="H27" s="26">
         <v>9.4582602133153362</v>
       </c>
-      <c r="I27" s="36"/>
+      <c r="I27" s="37"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
@@ -15021,7 +15043,7 @@
       <c r="H28" s="26">
         <v>9.4931271421144849</v>
       </c>
-      <c r="I28" s="36"/>
+      <c r="I28" s="37"/>
       <c r="J28" s="21"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -15049,7 +15071,7 @@
       <c r="H29" s="26">
         <v>9.5510599947217294</v>
       </c>
-      <c r="I29" s="36"/>
+      <c r="I29" s="37"/>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
@@ -15080,7 +15102,7 @@
       <c r="H30" s="26">
         <v>9.6562582805678048</v>
       </c>
-      <c r="I30" s="36"/>
+      <c r="I30" s="37"/>
       <c r="J30" s="21"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -15108,7 +15130,7 @@
       <c r="H31" s="26">
         <v>9.747806494192</v>
       </c>
-      <c r="I31" s="36"/>
+      <c r="I31" s="37"/>
       <c r="J31" s="21"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -15136,7 +15158,7 @@
       <c r="H32" s="26">
         <v>9.6522731177473311</v>
       </c>
-      <c r="I32" s="36"/>
+      <c r="I32" s="37"/>
       <c r="J32" s="21"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -15164,7 +15186,7 @@
       <c r="H33" s="26">
         <v>9.497746203493767</v>
       </c>
-      <c r="I33" s="36"/>
+      <c r="I33" s="37"/>
       <c r="J33" s="21"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -15192,7 +15214,7 @@
       <c r="H34" s="24">
         <v>9.4982302441665372</v>
       </c>
-      <c r="I34" s="37"/>
+      <c r="I34" s="38"/>
       <c r="J34" s="21"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">

--- a/Scripts/Prices regionalization.xlsx
+++ b/Scripts/Prices regionalization.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562D5297-5F84-427C-B858-9769622F51DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" firstSheet="3" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Wind LCOH countries" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="US" sheetId="10" r:id="rId12"/>
     <sheet name="PPP" sheetId="11" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -323,7 +323,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -370,127 +370,133 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2882,7 +2888,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
@@ -2900,7 +2906,7 @@
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+            <a:ext xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11B68518-FE97-4CBC-9A9F-C718C9D42B84}"/>
             </a:ext>
           </a:extLst>
@@ -2923,7 +2929,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
@@ -2941,7 +2947,7 @@
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+            <a:ext xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6E5868C-D252-44A8-A1A1-3BE678360CAC}"/>
             </a:ext>
           </a:extLst>
@@ -3265,15 +3271,15 @@
   <dimension ref="A1:X20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="12.5546875" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="10.88671875" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="6.6640625" customWidth="true"/>
+    <col min="10" max="10" width="6.6640625" customWidth="true"/>
+    <col min="11" max="11" width="6.6640625" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="B1" s="35">
         <v>2019</v>
       </c>
@@ -3293,7 +3299,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3328,7 +3334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3393,7 +3399,7 @@
         <v>6.4964778242637857</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3458,7 +3464,7 @@
         <v>6.8956619976553917</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -3523,7 +3529,7 @@
         <v>6.9016922742924907</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3588,7 +3594,7 @@
         <v>5.9491301804454206</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3653,7 +3659,7 @@
         <v>6.5573923196899164</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>64</v>
       </c>
@@ -3718,7 +3724,7 @@
         <v>6.7187500700264966</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -3783,7 +3789,7 @@
         <v>5.1531493311922816</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -3848,7 +3854,7 @@
         <v>6.21069922256887</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="B12">
         <f>(1-B9/B10)*100</f>
         <v>0</v>
@@ -3862,7 +3868,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="M13" s="30" t="s">
         <v>1</v>
       </c>
@@ -3908,7 +3914,7 @@
       </c>
       <c r="X13" s="31"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="M14" s="30" t="s">
         <v>2</v>
       </c>
@@ -3954,7 +3960,7 @@
       </c>
       <c r="X14" s="31"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="M15" s="30" t="s">
         <v>3</v>
       </c>
@@ -4000,7 +4006,7 @@
       </c>
       <c r="X15" s="31"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="M16" s="30" t="s">
         <v>4</v>
       </c>
@@ -4046,7 +4052,7 @@
       </c>
       <c r="X16" s="31"/>
     </row>
-    <row r="17" spans="13:24" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="M17" s="30" t="s">
         <v>5</v>
       </c>
@@ -4092,7 +4098,7 @@
       </c>
       <c r="X17" s="31"/>
     </row>
-    <row r="18" spans="13:24" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="M18" s="30" t="s">
         <v>64</v>
       </c>
@@ -4138,7 +4144,7 @@
       </c>
       <c r="X18" s="31"/>
     </row>
-    <row r="19" spans="13:24" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="M19" s="30" t="s">
         <v>6</v>
       </c>
@@ -4184,7 +4190,7 @@
       </c>
       <c r="X19" s="31"/>
     </row>
-    <row r="20" spans="13:24" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="N20" s="33">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -4243,12 +4249,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="16"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="7.6640625" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="4" max="9" width="7.6640625" customWidth="true"/>
+    <col min="10" max="10" width="7.6640625" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>62</v>
       </c>
@@ -4280,7 +4286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -4342,7 +4348,7 @@
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="16">
         <f>A2+1</f>
         <v>2</v>
@@ -4405,7 +4411,7 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="16">
         <f t="shared" ref="A4:A48" si="2">A3+1</f>
         <v>3</v>
@@ -4468,7 +4474,7 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="16">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -4531,7 +4537,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -4594,7 +4600,7 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -4657,7 +4663,7 @@
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="16">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -4720,7 +4726,7 @@
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -4783,7 +4789,7 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="16">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -4846,7 +4852,7 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="16">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -4909,7 +4915,7 @@
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="16">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -4972,7 +4978,7 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="16">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -5035,7 +5041,7 @@
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="16">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -5098,7 +5104,7 @@
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -5161,7 +5167,7 @@
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="16">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -5224,7 +5230,7 @@
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -5287,7 +5293,7 @@
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="16">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -5350,7 +5356,7 @@
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="16">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -5413,7 +5419,7 @@
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="16">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -5476,7 +5482,7 @@
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="16">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -5539,7 +5545,7 @@
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="16">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -5602,7 +5608,7 @@
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="16">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -5665,7 +5671,7 @@
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="16">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -5728,7 +5734,7 @@
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="16">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -5791,7 +5797,7 @@
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="16">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -5854,7 +5860,7 @@
       <c r="T26" s="8"/>
       <c r="U26" s="8"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -5917,7 +5923,7 @@
       <c r="T27" s="8"/>
       <c r="U27" s="8"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="16">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -5980,7 +5986,7 @@
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="16">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -6043,7 +6049,7 @@
       <c r="T29" s="8"/>
       <c r="U29" s="8"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="16">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -6106,7 +6112,7 @@
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="16">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -6169,7 +6175,7 @@
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="16">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -6232,7 +6238,7 @@
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="16">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -6295,7 +6301,7 @@
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="16">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -6358,7 +6364,7 @@
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="16">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -6421,7 +6427,7 @@
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="16">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -6484,7 +6490,7 @@
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="16">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -6547,7 +6553,7 @@
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="16">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -6619,7 +6625,7 @@
       <c r="Y38" s="31"/>
       <c r="Z38" s="31"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="16">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -6682,7 +6688,7 @@
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="16">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -6745,7 +6751,7 @@
       <c r="T40" s="8"/>
       <c r="U40" s="8"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="16">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -6808,7 +6814,7 @@
       <c r="T41" s="8"/>
       <c r="U41" s="8"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="16">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -6871,7 +6877,7 @@
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="16">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -6934,7 +6940,7 @@
       <c r="T43" s="8"/>
       <c r="U43" s="8"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="16">
         <f t="shared" si="2"/>
         <v>43</v>
@@ -6997,7 +7003,7 @@
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="16">
         <f t="shared" si="2"/>
         <v>44</v>
@@ -7060,7 +7066,7 @@
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="16">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -7123,7 +7129,7 @@
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="16">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -7186,7 +7192,7 @@
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="16">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -7259,13 +7265,13 @@
   <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="true" customWidth="true"/>
+    <col min="4" max="7" width="7.5546875" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="10.88671875" bestFit="true" customWidth="true"/>
+    <col min="9" max="9" width="7.5546875" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>62</v>
       </c>
@@ -7294,7 +7300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -7351,7 +7357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="16">
         <f>A2+1</f>
         <v>2</v>
@@ -7409,7 +7415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="16">
         <f t="shared" ref="A4:A48" si="2">A3+1</f>
         <v>3</v>
@@ -7467,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="16">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7525,7 +7531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7583,7 +7589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7641,7 +7647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="16">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7699,7 +7705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7757,7 +7763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="16">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7815,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="16">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7873,7 +7879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="16">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7931,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="16">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -7989,7 +7995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="16">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -8047,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -8105,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="16">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -8163,7 +8169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -8221,7 +8227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="16">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -8279,7 +8285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="16">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -8337,7 +8343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="16">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -8395,7 +8401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="16">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -8453,7 +8459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="16">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -8511,7 +8517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="16">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -8569,7 +8575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="16">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -8627,7 +8633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="16">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -8685,7 +8691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="16">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -8743,7 +8749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -8801,7 +8807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="16">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -8859,7 +8865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="16">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -8917,7 +8923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="16">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -8975,7 +8981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="16">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -9033,7 +9039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="16">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -9091,7 +9097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="16">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -9149,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="16">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -9207,7 +9213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="16">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -9265,7 +9271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="16">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -9323,7 +9329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="16">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -9381,7 +9387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="16">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -9447,7 +9453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="16">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -9505,7 +9511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="16">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -9563,7 +9569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="16">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -9621,7 +9627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="16">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -9679,7 +9685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="16">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -9737,7 +9743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="16">
         <f t="shared" si="2"/>
         <v>43</v>
@@ -9795,7 +9801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="16">
         <f t="shared" si="2"/>
         <v>44</v>
@@ -9853,7 +9859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="16">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -9911,7 +9917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="16">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -9969,7 +9975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="16">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -10037,17 +10043,17 @@
   <dimension ref="A1:U53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="true" customWidth="true"/>
+    <col min="5" max="5" width="13.5546875" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="6.7109375" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="7.7109375" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="7.7109375" bestFit="true" customWidth="true"/>
+    <col min="9" max="9" width="12.44140625" bestFit="true" customWidth="true"/>
+    <col min="10" max="10" width="13.21875" bestFit="true" customWidth="true"/>
+    <col min="11" max="11" width="13.109375" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>62</v>
       </c>
@@ -10106,7 +10112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -10166,7 +10172,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="17">
         <f>A2+1</f>
         <v>2</v>
@@ -10227,7 +10233,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="17">
         <f t="shared" ref="A4:A48" si="1">A3+1</f>
         <v>3</v>
@@ -10288,7 +10294,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="17">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -10339,7 +10345,7 @@
       <c r="R5" s="18"/>
       <c r="S5" s="18"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -10376,7 +10382,7 @@
         <v>2157.0404745719552</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="17">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -10413,7 +10419,7 @@
         <v>2156.2344779048158</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="17">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -10450,7 +10456,7 @@
         <v>2156.7595778255131</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="17">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -10487,7 +10493,7 @@
         <v>2154.7919082156136</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -10524,7 +10530,7 @@
         <v>2156.6159618651445</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -10561,7 +10567,7 @@
         <v>2154.5191495439794</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -10598,7 +10604,7 @@
         <v>2155.7283031142078</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -10635,7 +10641,7 @@
         <v>2152.8490090770738</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -10672,7 +10678,7 @@
         <v>2140.8894724165611</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -10709,7 +10715,7 @@
         <v>2139.9384576468083</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -10746,7 +10752,7 @@
         <v>2139.0787809409962</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -10783,7 +10789,7 @@
         <v>2139.1509701385235</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -10820,7 +10826,7 @@
         <v>2140.4480416755728</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="17">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -10857,7 +10863,7 @@
         <v>2140.1324378104073</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="17">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -10894,7 +10900,7 @@
         <v>2140.7172260215475</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -10931,7 +10937,7 @@
         <v>2144.4634149235972</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -10968,7 +10974,7 @@
         <v>2140.9480116254945</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -11005,7 +11011,7 @@
         <v>2142.5535090519793</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="17">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -11042,7 +11048,7 @@
         <v>2144.6935076006444</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -11079,7 +11085,7 @@
         <v>2144.0785195481089</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -11116,7 +11122,7 @@
         <v>2126.3298582536563</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -11153,7 +11159,7 @@
         <v>2140.777617987741</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -11190,7 +11196,7 @@
         <v>2122.4745183081895</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="17">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -11227,7 +11233,7 @@
         <v>2122.6422704618403</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="17">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -11264,7 +11270,7 @@
         <v>2126.296494628355</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="17">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -11301,7 +11307,7 @@
         <v>2129.2946504429428</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="17">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -11338,7 +11344,7 @@
         <v>2133.6478522332204</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="17">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -11375,7 +11381,7 @@
         <v>2135.5688253682638</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="17">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -11412,7 +11418,7 @@
         <v>2142.4788619233004</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="17">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -11449,7 +11455,7 @@
         <v>2144.8311314875759</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="17">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -11486,7 +11492,7 @@
         <v>2140.685898706457</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="17">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -11523,7 +11529,7 @@
         <v>2132.43271755863</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -11560,7 +11566,7 @@
         <v>2493.161468084445</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="17">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -11597,7 +11603,7 @@
         <v>2495.5225230375727</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="17">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -11634,7 +11640,7 @@
         <v>2498.122205172866</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="17">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -11671,7 +11677,7 @@
         <v>2511.2120397095041</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="17">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -11708,7 +11714,7 @@
         <v>2524.2025316934823</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="17">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -11745,7 +11751,7 @@
         <v>2522.3170465772955</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="17">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -11782,7 +11788,7 @@
         <v>2519.6986152583786</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="17">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -11819,7 +11825,7 @@
         <v>2529.5085794029592</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="17">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -11856,7 +11862,7 @@
         <v>2520.537885400583</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="17">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -11893,7 +11899,7 @@
         <v>2504.6693147162869</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="17">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -11930,19 +11936,19 @@
         <v>2503.2367457527521</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="49" x14ac:dyDescent="0.3">
       <c r="C49" s="8"/>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="50" x14ac:dyDescent="0.3">
       <c r="C50" s="8"/>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="51" x14ac:dyDescent="0.3">
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="52" x14ac:dyDescent="0.3">
       <c r="C52" s="8"/>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="53" x14ac:dyDescent="0.3">
       <c r="C53" s="8"/>
     </row>
   </sheetData>
@@ -11955,13 +11961,13 @@
   <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.5546875" bestFit="true" customWidth="true"/>
+    <col min="9" max="9" width="11" bestFit="true" customWidth="true"/>
+    <col min="10" max="11" width="9.5546875" bestFit="true" customWidth="true"/>
+    <col min="12" max="12" width="13.33203125" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>78</v>
       </c>
@@ -11999,7 +12005,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>2019</v>
       </c>
@@ -12035,7 +12041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>2020</v>
       </c>
@@ -12070,7 +12076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>2021</v>
       </c>
@@ -12105,7 +12111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>2022</v>
       </c>
@@ -12140,7 +12146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>78</v>
       </c>
@@ -12178,7 +12184,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="19">
         <v>2019</v>
       </c>
@@ -12213,7 +12219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
         <v>2020</v>
       </c>
@@ -12248,7 +12254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="19">
         <v>2021</v>
       </c>
@@ -12283,7 +12289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
         <v>2022</v>
       </c>
@@ -12318,7 +12324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -12331,7 +12337,7 @@
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>79</v>
       </c>
@@ -12369,7 +12375,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
         <v>2019</v>
       </c>
@@ -12414,7 +12420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
         <v>2020</v>
       </c>
@@ -12459,7 +12465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>2021</v>
       </c>
@@ -12504,7 +12510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
         <v>2022</v>
       </c>
@@ -12559,14 +12565,14 @@
   <dimension ref="A1:V27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" customWidth="1"/>
-    <col min="10" max="11" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="12.5546875" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="7.6640625" customWidth="true"/>
+    <col min="10" max="11" width="7.6640625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="B1" s="35">
         <v>2019</v>
       </c>
@@ -12586,7 +12592,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -12621,7 +12627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -12656,7 +12662,7 @@
         <v>10.530004206601616</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
@@ -12691,7 +12697,7 @@
         <v>9.7107722150761919</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -12735,7 +12741,7 @@
       <c r="U5" s="13"/>
       <c r="V5" s="13"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>64</v>
       </c>
@@ -12779,7 +12785,7 @@
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
@@ -12823,7 +12829,7 @@
       <c r="U7" s="13"/>
       <c r="V7" s="13"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>63</v>
       </c>
@@ -12867,7 +12873,7 @@
       <c r="U8" s="13"/>
       <c r="V8" s="13"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
@@ -12911,7 +12917,7 @@
       <c r="U9" s="13"/>
       <c r="V9" s="13"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="C10" s="10"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
@@ -12923,7 +12929,7 @@
       <c r="U10" s="13"/>
       <c r="V10" s="13"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="B11">
         <f>(1-B7/B9)*100</f>
         <v>16.029411764705891</v>
@@ -12946,7 +12952,7 @@
       <c r="U11" s="13"/>
       <c r="V11" s="13"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
@@ -12957,7 +12963,7 @@
       <c r="U12" s="13"/>
       <c r="V12" s="13"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="4"/>
       <c r="C13" s="12"/>
@@ -12979,7 +12985,7 @@
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="4"/>
       <c r="C14" s="12"/>
@@ -13001,7 +13007,7 @@
       <c r="U14" s="13"/>
       <c r="V14" s="13"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="12"/>
@@ -13023,7 +13029,7 @@
       <c r="U15" s="13"/>
       <c r="V15" s="13"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
@@ -13034,7 +13040,7 @@
       <c r="U16" s="13"/>
       <c r="V16" s="13"/>
     </row>
-    <row r="17" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
@@ -13045,7 +13051,7 @@
       <c r="U17" s="13"/>
       <c r="V17" s="13"/>
     </row>
-    <row r="18" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
@@ -13056,7 +13062,7 @@
       <c r="U18" s="13"/>
       <c r="V18" s="13"/>
     </row>
-    <row r="19" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
@@ -13067,7 +13073,7 @@
       <c r="U19" s="13"/>
       <c r="V19" s="13"/>
     </row>
-    <row r="20" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
@@ -13078,7 +13084,7 @@
       <c r="U20" s="13"/>
       <c r="V20" s="13"/>
     </row>
-    <row r="21" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
@@ -13089,7 +13095,7 @@
       <c r="U21" s="13"/>
       <c r="V21" s="13"/>
     </row>
-    <row r="22" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -13100,7 +13106,7 @@
       <c r="U22" s="13"/>
       <c r="V22" s="13"/>
     </row>
-    <row r="23" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
@@ -13111,7 +13117,7 @@
       <c r="U23" s="13"/>
       <c r="V23" s="13"/>
     </row>
-    <row r="24" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
@@ -13122,7 +13128,7 @@
       <c r="U24" s="13"/>
       <c r="V24" s="13"/>
     </row>
-    <row r="25" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="N25" s="13"/>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
@@ -13133,7 +13139,7 @@
       <c r="U25" s="13"/>
       <c r="V25" s="13"/>
     </row>
-    <row r="26" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="N26" s="13"/>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
@@ -13144,7 +13150,7 @@
       <c r="U26" s="13"/>
       <c r="V26" s="13"/>
     </row>
-    <row r="27" spans="14:22" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
@@ -13170,12 +13176,12 @@
   <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="true" customWidth="true"/>
+    <col min="2" max="9" width="6.6640625" bestFit="true" customWidth="true"/>
+    <col min="10" max="10" width="14.109375" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>9</v>
       </c>
@@ -13213,7 +13219,7 @@
       <c r="Q1" s="22"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>47</v>
       </c>
@@ -13245,7 +13251,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>48</v>
       </c>
@@ -13275,7 +13281,7 @@
       </c>
       <c r="J3" s="39"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>49</v>
       </c>
@@ -13305,7 +13311,7 @@
       </c>
       <c r="J4" s="39"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>50</v>
       </c>
@@ -13335,7 +13341,7 @@
       </c>
       <c r="J5" s="39"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>51</v>
       </c>
@@ -13365,7 +13371,7 @@
       </c>
       <c r="J6" s="39"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>52</v>
       </c>
@@ -13395,7 +13401,7 @@
       </c>
       <c r="J7" s="39"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>53</v>
       </c>
@@ -13425,7 +13431,7 @@
       </c>
       <c r="J8" s="39"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>54</v>
       </c>
@@ -13455,7 +13461,7 @@
       </c>
       <c r="J9" s="39"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>55</v>
       </c>
@@ -13485,7 +13491,7 @@
       </c>
       <c r="J10" s="39"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>56</v>
       </c>
@@ -13515,7 +13521,7 @@
       </c>
       <c r="J11" s="39"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
@@ -13545,7 +13551,7 @@
       </c>
       <c r="J12" s="40"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>47</v>
       </c>
@@ -13577,7 +13583,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>48</v>
       </c>
@@ -13607,7 +13613,7 @@
       </c>
       <c r="J14" s="39"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
         <v>49</v>
       </c>
@@ -13637,7 +13643,7 @@
       </c>
       <c r="J15" s="39"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>50</v>
       </c>
@@ -13667,7 +13673,7 @@
       </c>
       <c r="J16" s="39"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>51</v>
       </c>
@@ -13697,7 +13703,7 @@
       </c>
       <c r="J17" s="39"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>52</v>
       </c>
@@ -13727,7 +13733,7 @@
       </c>
       <c r="J18" s="39"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>53</v>
       </c>
@@ -13757,7 +13763,7 @@
       </c>
       <c r="J19" s="39"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>54</v>
       </c>
@@ -13787,7 +13793,7 @@
       </c>
       <c r="J20" s="39"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>55</v>
       </c>
@@ -13817,7 +13823,7 @@
       </c>
       <c r="J21" s="39"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>56</v>
       </c>
@@ -13847,7 +13853,7 @@
       </c>
       <c r="J22" s="39"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>57</v>
       </c>
@@ -13877,7 +13883,7 @@
       </c>
       <c r="J23" s="40"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
         <v>47</v>
       </c>
@@ -13909,7 +13915,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>48</v>
       </c>
@@ -13939,7 +13945,7 @@
       </c>
       <c r="J25" s="37"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>49</v>
       </c>
@@ -13969,7 +13975,7 @@
       </c>
       <c r="J26" s="37"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
         <v>50</v>
       </c>
@@ -13999,7 +14005,7 @@
       </c>
       <c r="J27" s="37"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>51</v>
       </c>
@@ -14029,7 +14035,7 @@
       </c>
       <c r="J28" s="37"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
         <v>52</v>
       </c>
@@ -14059,7 +14065,7 @@
       </c>
       <c r="J29" s="37"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>53</v>
       </c>
@@ -14089,7 +14095,7 @@
       </c>
       <c r="J30" s="37"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
         <v>54</v>
       </c>
@@ -14119,7 +14125,7 @@
       </c>
       <c r="J31" s="37"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>55</v>
       </c>
@@ -14149,7 +14155,7 @@
       </c>
       <c r="J32" s="37"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
         <v>56</v>
       </c>
@@ -14179,7 +14185,7 @@
       </c>
       <c r="J33" s="37"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>57</v>
       </c>
@@ -14225,17 +14231,17 @@
   <dimension ref="A1:AG40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="7.6640625" customWidth="true"/>
+    <col min="3" max="4" width="6.6640625" customWidth="true"/>
+    <col min="5" max="5" width="7.6640625" customWidth="true"/>
+    <col min="6" max="6" width="6.6640625" customWidth="true"/>
+    <col min="7" max="7" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="6.6640625" customWidth="true"/>
+    <col min="9" max="9" width="14.109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>9</v>
       </c>
@@ -14262,7 +14268,7 @@
       </c>
       <c r="I1" s="29"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>47</v>
       </c>
@@ -14298,7 +14304,7 @@
       <c r="O2" s="22"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>48</v>
       </c>
@@ -14325,7 +14331,7 @@
       </c>
       <c r="I3" s="39"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>49</v>
       </c>
@@ -14361,7 +14367,7 @@
       <c r="AF4" s="22"/>
       <c r="AG4" s="22"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>50</v>
       </c>
@@ -14397,7 +14403,7 @@
       <c r="AF5" s="22"/>
       <c r="AG5" s="22"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>51</v>
       </c>
@@ -14433,7 +14439,7 @@
       <c r="AF6" s="22"/>
       <c r="AG6" s="22"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>52</v>
       </c>
@@ -14460,7 +14466,7 @@
       </c>
       <c r="I7" s="39"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>53</v>
       </c>
@@ -14487,7 +14493,7 @@
       </c>
       <c r="I8" s="39"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>54</v>
       </c>
@@ -14514,7 +14520,7 @@
       </c>
       <c r="I9" s="39"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>55</v>
       </c>
@@ -14541,7 +14547,7 @@
       </c>
       <c r="I10" s="39"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>56</v>
       </c>
@@ -14568,7 +14574,7 @@
       </c>
       <c r="I11" s="39"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
@@ -14595,7 +14601,7 @@
       </c>
       <c r="I12" s="40"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>47</v>
       </c>
@@ -14631,7 +14637,7 @@
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>48</v>
       </c>
@@ -14658,7 +14664,7 @@
       </c>
       <c r="I14" s="39"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
         <v>49</v>
       </c>
@@ -14685,7 +14691,7 @@
       </c>
       <c r="I15" s="39"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>50</v>
       </c>
@@ -14712,7 +14718,7 @@
       </c>
       <c r="I16" s="39"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>51</v>
       </c>
@@ -14739,7 +14745,7 @@
       </c>
       <c r="I17" s="39"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>52</v>
       </c>
@@ -14766,7 +14772,7 @@
       </c>
       <c r="I18" s="39"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>53</v>
       </c>
@@ -14793,7 +14799,7 @@
       </c>
       <c r="I19" s="39"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>54</v>
       </c>
@@ -14820,7 +14826,7 @@
       </c>
       <c r="I20" s="39"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>55</v>
       </c>
@@ -14847,7 +14853,7 @@
       </c>
       <c r="I21" s="39"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>56</v>
       </c>
@@ -14874,7 +14880,7 @@
       </c>
       <c r="I22" s="39"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>57</v>
       </c>
@@ -14901,7 +14907,7 @@
       </c>
       <c r="I23" s="40"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
         <v>47</v>
       </c>
@@ -14937,7 +14943,7 @@
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>48</v>
       </c>
@@ -14964,7 +14970,7 @@
       </c>
       <c r="I25" s="37"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>49</v>
       </c>
@@ -14991,7 +14997,7 @@
       </c>
       <c r="I26" s="37"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
         <v>50</v>
       </c>
@@ -15018,7 +15024,7 @@
       </c>
       <c r="I27" s="37"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>51</v>
       </c>
@@ -15046,7 +15052,7 @@
       <c r="I28" s="37"/>
       <c r="J28" s="21"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
         <v>52</v>
       </c>
@@ -15077,7 +15083,7 @@
       <c r="L29" s="21"/>
       <c r="M29" s="21"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>53</v>
       </c>
@@ -15105,7 +15111,7 @@
       <c r="I30" s="37"/>
       <c r="J30" s="21"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
         <v>54</v>
       </c>
@@ -15133,7 +15139,7 @@
       <c r="I31" s="37"/>
       <c r="J31" s="21"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>55</v>
       </c>
@@ -15161,7 +15167,7 @@
       <c r="I32" s="37"/>
       <c r="J32" s="21"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
         <v>56</v>
       </c>
@@ -15189,7 +15195,7 @@
       <c r="I33" s="37"/>
       <c r="J33" s="21"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>57</v>
       </c>
@@ -15217,7 +15223,7 @@
       <c r="I34" s="38"/>
       <c r="J34" s="21"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
       <c r="G35" s="21"/>
@@ -15225,7 +15231,7 @@
       <c r="I35" s="21"/>
       <c r="J35" s="21"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21"/>
@@ -15233,7 +15239,7 @@
       <c r="I36" s="21"/>
       <c r="J36" s="21"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
@@ -15241,13 +15247,13 @@
       <c r="I37" s="21"/>
       <c r="J37" s="21"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="E38" s="21"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="E39" s="21"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -15266,12 +15272,12 @@
   <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="true" customWidth="true"/>
+    <col min="2" max="3" width="8.33203125" bestFit="true" customWidth="true"/>
+    <col min="9" max="9" width="10.88671875" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -15303,7 +15309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -15336,7 +15342,7 @@
         <v>49.41</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -15369,7 +15375,7 @@
         <v>42.81</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -15402,7 +15408,7 @@
         <v>30.61</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -15435,7 +15441,7 @@
         <v>36.97</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -15468,7 +15474,7 @@
         <v>37.83</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -15501,7 +15507,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
@@ -15534,7 +15540,7 @@
         <v>39.71</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
@@ -15567,7 +15573,7 @@
         <v>36.82</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>19</v>
       </c>
@@ -15600,7 +15606,7 @@
         <v>35.770000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -15633,7 +15639,7 @@
         <v>36.950000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>21</v>
       </c>
@@ -15666,7 +15672,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>22</v>
       </c>
@@ -15699,7 +15705,7 @@
         <v>31.97</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -15732,7 +15738,7 @@
         <v>34.979999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
@@ -15765,7 +15771,7 @@
         <v>21.91</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
@@ -15798,7 +15804,7 @@
         <v>22.52</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
@@ -15831,7 +15837,7 @@
         <v>17.05</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
@@ -15864,7 +15870,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
@@ -15897,7 +15903,7 @@
         <v>26.23</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -15930,7 +15936,7 @@
         <v>30.07</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
@@ -15963,7 +15969,7 @@
         <v>34.89</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>31</v>
       </c>
@@ -15996,7 +16002,7 @@
         <v>43.68</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>32</v>
       </c>
@@ -16029,7 +16035,7 @@
         <v>33.96</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>33</v>
       </c>
@@ -16062,7 +16068,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>34</v>
       </c>
@@ -16095,7 +16101,7 @@
         <v>43.55</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>35</v>
       </c>
@@ -16128,7 +16134,7 @@
         <v>52.79</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>36</v>
       </c>
@@ -16161,7 +16167,7 @@
         <v>48.71</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
@@ -16194,7 +16200,7 @@
         <v>47.18</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
@@ -16227,7 +16233,7 @@
         <v>53.66</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
@@ -16260,7 +16266,7 @@
         <v>53.33</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
@@ -16293,7 +16299,7 @@
         <v>74.13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
@@ -16326,7 +16332,7 @@
         <v>81.290000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
@@ -16359,7 +16365,7 @@
         <v>82.81</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
@@ -16392,7 +16398,7 @@
         <v>128.34</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>44</v>
       </c>
@@ -16425,7 +16431,7 @@
         <v>139.54</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>45</v>
       </c>
@@ -16458,7 +16464,7 @@
         <v>176.25</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>46</v>
       </c>
@@ -16491,7 +16497,7 @@
         <v>220.96</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>47</v>
       </c>
@@ -16524,7 +16530,7 @@
         <v>167.87</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>48</v>
       </c>
@@ -16557,7 +16563,7 @@
         <v>128.78</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>49</v>
       </c>
@@ -16590,7 +16596,7 @@
         <v>251.76</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>50</v>
       </c>
@@ -16623,7 +16629,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>51</v>
       </c>
@@ -16656,7 +16662,7 @@
         <v>177.51</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>52</v>
       </c>
@@ -16689,7 +16695,7 @@
         <v>218.18</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>53</v>
       </c>
@@ -16722,7 +16728,7 @@
         <v>315.26</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>54</v>
       </c>
@@ -16755,7 +16761,7 @@
         <v>469.35</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>55</v>
       </c>
@@ -16788,7 +16794,7 @@
         <v>360.18</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>56</v>
       </c>
@@ -16821,7 +16827,7 @@
         <v>157.78</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>57</v>
       </c>
@@ -16865,13 +16871,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="10"/>
-    <col min="3" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="50" width="11.6640625" customWidth="1"/>
+    <col min="3" max="9" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="10" max="10" width="10.88671875" bestFit="true" customWidth="true"/>
+    <col min="11" max="11" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="12" max="50" width="11.6640625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
@@ -16906,7 +16912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -16978,7 +16984,7 @@
       </c>
       <c r="V2" s="8"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <f>A2+1</f>
         <v>2</v>
@@ -17051,7 +17057,7 @@
       </c>
       <c r="V3" s="8"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <f t="shared" ref="A4:A48" si="10">A3+1</f>
         <v>3</v>
@@ -17124,7 +17130,7 @@
       </c>
       <c r="V4" s="8"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <f t="shared" si="10"/>
         <v>4</v>
@@ -17197,7 +17203,7 @@
       </c>
       <c r="V5" s="8"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <f t="shared" si="10"/>
         <v>5</v>
@@ -17270,7 +17276,7 @@
       </c>
       <c r="V6" s="8"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <f t="shared" si="10"/>
         <v>6</v>
@@ -17343,7 +17349,7 @@
       </c>
       <c r="V7" s="8"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <f t="shared" si="10"/>
         <v>7</v>
@@ -17416,7 +17422,7 @@
       </c>
       <c r="V8" s="8"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <f t="shared" si="10"/>
         <v>8</v>
@@ -17489,7 +17495,7 @@
       </c>
       <c r="V9" s="8"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <f t="shared" si="10"/>
         <v>9</v>
@@ -17562,7 +17568,7 @@
       </c>
       <c r="V10" s="8"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <f t="shared" si="10"/>
         <v>10</v>
@@ -17635,7 +17641,7 @@
       </c>
       <c r="V11" s="8"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <f t="shared" si="10"/>
         <v>11</v>
@@ -17708,7 +17714,7 @@
       </c>
       <c r="V12" s="8"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <f t="shared" si="10"/>
         <v>12</v>
@@ -17781,7 +17787,7 @@
       </c>
       <c r="V13" s="8"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <f t="shared" si="10"/>
         <v>13</v>
@@ -17854,7 +17860,7 @@
       </c>
       <c r="V14" s="8"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <f t="shared" si="10"/>
         <v>14</v>
@@ -17927,7 +17933,7 @@
       </c>
       <c r="V15" s="8"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <f t="shared" si="10"/>
         <v>15</v>
@@ -18000,7 +18006,7 @@
       </c>
       <c r="V16" s="8"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -18073,7 +18079,7 @@
       </c>
       <c r="V17" s="8"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <f t="shared" si="10"/>
         <v>17</v>
@@ -18146,7 +18152,7 @@
       </c>
       <c r="V18" s="8"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <f t="shared" si="10"/>
         <v>18</v>
@@ -18219,7 +18225,7 @@
       </c>
       <c r="V19" s="8"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="10"/>
         <v>19</v>
@@ -18292,7 +18298,7 @@
       </c>
       <c r="V20" s="8"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <f t="shared" si="10"/>
         <v>20</v>
@@ -18365,7 +18371,7 @@
       </c>
       <c r="V21" s="8"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <f t="shared" si="10"/>
         <v>21</v>
@@ -18438,7 +18444,7 @@
       </c>
       <c r="V22" s="8"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <f t="shared" si="10"/>
         <v>22</v>
@@ -18511,7 +18517,7 @@
       </c>
       <c r="V23" s="8"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <f t="shared" si="10"/>
         <v>23</v>
@@ -18584,7 +18590,7 @@
       </c>
       <c r="V24" s="8"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -18657,7 +18663,7 @@
       </c>
       <c r="V25" s="8"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -18730,7 +18736,7 @@
       </c>
       <c r="V26" s="8"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -18803,7 +18809,7 @@
       </c>
       <c r="V27" s="8"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -18876,7 +18882,7 @@
       </c>
       <c r="V28" s="8"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -18949,7 +18955,7 @@
       </c>
       <c r="V29" s="8"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -19022,7 +19028,7 @@
       </c>
       <c r="V30" s="8"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -19095,7 +19101,7 @@
       </c>
       <c r="V31" s="8"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -19168,7 +19174,7 @@
       </c>
       <c r="V32" s="8"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -19241,7 +19247,7 @@
       </c>
       <c r="V33" s="8"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -19314,7 +19320,7 @@
       </c>
       <c r="V34" s="8"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -19387,7 +19393,7 @@
       </c>
       <c r="V35" s="8"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -19460,7 +19466,7 @@
       </c>
       <c r="V36" s="8"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -19533,7 +19539,7 @@
       </c>
       <c r="V37" s="8"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -19606,7 +19612,7 @@
       </c>
       <c r="V38" s="8"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -19679,7 +19685,7 @@
       </c>
       <c r="V39" s="8"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -19752,7 +19758,7 @@
       </c>
       <c r="V40" s="8"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -19825,7 +19831,7 @@
       </c>
       <c r="V41" s="8"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -19898,7 +19904,7 @@
       </c>
       <c r="V42" s="8"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -19971,7 +19977,7 @@
       </c>
       <c r="V43" s="8"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -20044,7 +20050,7 @@
       </c>
       <c r="V44" s="8"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -20117,7 +20123,7 @@
       </c>
       <c r="V45" s="8"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -20190,7 +20196,7 @@
       </c>
       <c r="V46" s="8"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <f t="shared" si="10"/>
         <v>46</v>
@@ -20263,7 +20269,7 @@
       </c>
       <c r="V47" s="8"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -20348,12 +20354,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="10"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="7.6640625" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="4" max="9" width="7.6640625" customWidth="true"/>
+    <col min="10" max="10" width="7.6640625" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
@@ -20385,7 +20391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -20449,7 +20455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <f>A2+1</f>
         <v>2</v>
@@ -20514,7 +20520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <f t="shared" ref="A4:A48" si="9">A3+1</f>
         <v>3</v>
@@ -20579,7 +20585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <f t="shared" si="9"/>
         <v>4</v>
@@ -20644,7 +20650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <f t="shared" si="9"/>
         <v>5</v>
@@ -20709,7 +20715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <f t="shared" si="9"/>
         <v>6</v>
@@ -20774,7 +20780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <f t="shared" si="9"/>
         <v>7</v>
@@ -20839,7 +20845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <f t="shared" si="9"/>
         <v>8</v>
@@ -20904,7 +20910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <f t="shared" si="9"/>
         <v>9</v>
@@ -20969,7 +20975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <f t="shared" si="9"/>
         <v>10</v>
@@ -21034,7 +21040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <f t="shared" si="9"/>
         <v>11</v>
@@ -21099,7 +21105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <f t="shared" si="9"/>
         <v>12</v>
@@ -21164,7 +21170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
@@ -21229,7 +21235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
@@ -21294,7 +21300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <f t="shared" si="9"/>
         <v>15</v>
@@ -21359,7 +21365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <f t="shared" si="9"/>
         <v>16</v>
@@ -21424,7 +21430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <f t="shared" si="9"/>
         <v>17</v>
@@ -21489,7 +21495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <f t="shared" si="9"/>
         <v>18</v>
@@ -21554,7 +21560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="9"/>
         <v>19</v>
@@ -21619,7 +21625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <f t="shared" si="9"/>
         <v>20</v>
@@ -21684,7 +21690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <f t="shared" si="9"/>
         <v>21</v>
@@ -21749,7 +21755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <f t="shared" si="9"/>
         <v>22</v>
@@ -21814,7 +21820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <f t="shared" si="9"/>
         <v>23</v>
@@ -21879,7 +21885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -21944,7 +21950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -22009,7 +22015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -22074,7 +22080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -22139,7 +22145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -22204,7 +22210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -22269,7 +22275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -22334,7 +22340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -22399,7 +22405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -22464,7 +22470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -22529,7 +22535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -22594,7 +22600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <f t="shared" si="9"/>
         <v>35</v>
@@ -22659,7 +22665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -22724,7 +22730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -22790,7 +22796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -22855,7 +22861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -22920,7 +22926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -22985,7 +22991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -23050,7 +23056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -23115,7 +23121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -23180,7 +23186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -23245,7 +23251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <f t="shared" si="9"/>
         <v>45</v>
@@ -23310,7 +23316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <f t="shared" si="9"/>
         <v>46</v>
@@ -23375,7 +23381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -23450,10 +23456,10 @@
   <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="7.6640625" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
@@ -23482,7 +23488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -23539,7 +23545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <f>A2+1</f>
         <v>2</v>
@@ -23597,7 +23603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <f t="shared" ref="A4:A48" si="8">A3+1</f>
         <v>3</v>
@@ -23655,7 +23661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <f t="shared" si="8"/>
         <v>4</v>
@@ -23713,7 +23719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -23771,7 +23777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -23829,7 +23835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <f t="shared" si="8"/>
         <v>7</v>
@@ -23887,7 +23893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <f t="shared" si="8"/>
         <v>8</v>
@@ -23945,7 +23951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <f t="shared" si="8"/>
         <v>9</v>
@@ -24003,7 +24009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <f t="shared" si="8"/>
         <v>10</v>
@@ -24061,7 +24067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -24119,7 +24125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <f t="shared" si="8"/>
         <v>12</v>
@@ -24177,7 +24183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <f t="shared" si="8"/>
         <v>13</v>
@@ -24235,7 +24241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -24293,7 +24299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <f t="shared" si="8"/>
         <v>15</v>
@@ -24351,7 +24357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <f t="shared" si="8"/>
         <v>16</v>
@@ -24409,7 +24415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <f t="shared" si="8"/>
         <v>17</v>
@@ -24467,7 +24473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <f t="shared" si="8"/>
         <v>18</v>
@@ -24525,7 +24531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <f t="shared" si="8"/>
         <v>19</v>
@@ -24583,7 +24589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <f t="shared" si="8"/>
         <v>20</v>
@@ -24641,7 +24647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <f t="shared" si="8"/>
         <v>21</v>
@@ -24699,7 +24705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <f t="shared" si="8"/>
         <v>22</v>
@@ -24757,7 +24763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <f t="shared" si="8"/>
         <v>23</v>
@@ -24815,7 +24821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <f t="shared" si="8"/>
         <v>24</v>
@@ -24873,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <f t="shared" si="8"/>
         <v>25</v>
@@ -24931,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <f t="shared" si="8"/>
         <v>26</v>
@@ -24989,7 +24995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -25047,7 +25053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -25105,7 +25111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -25163,7 +25169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -25221,7 +25227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <f t="shared" si="8"/>
         <v>31</v>
@@ -25279,7 +25285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -25337,7 +25343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <f t="shared" si="8"/>
         <v>33</v>
@@ -25395,7 +25401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <f t="shared" si="8"/>
         <v>34</v>
@@ -25453,7 +25459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <f t="shared" si="8"/>
         <v>35</v>
@@ -25511,7 +25517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <f t="shared" si="8"/>
         <v>36</v>
@@ -25569,7 +25575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <f t="shared" si="8"/>
         <v>37</v>
@@ -25629,7 +25635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <f t="shared" si="8"/>
         <v>38</v>
@@ -25687,7 +25693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <f t="shared" si="8"/>
         <v>39</v>
@@ -25745,7 +25751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <f t="shared" si="8"/>
         <v>40</v>
@@ -25803,7 +25809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -25861,7 +25867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -25919,7 +25925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -25977,7 +25983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -26035,7 +26041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -26093,7 +26099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="11">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -26151,7 +26157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -26220,14 +26226,14 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="15"/>
-    <col min="3" max="8" width="7.6640625" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="50" width="11.6640625" customWidth="1"/>
+    <col min="3" max="8" width="7.6640625" customWidth="true"/>
+    <col min="9" max="9" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="10" max="10" width="10.88671875" bestFit="true" customWidth="true"/>
+    <col min="11" max="11" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="12" max="50" width="11.6640625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>62</v>
       </c>
@@ -26262,7 +26268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -26333,7 +26339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="15">
         <f>A2+1</f>
         <v>2</v>
@@ -26405,7 +26411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <f t="shared" ref="A4:A48" si="1">A3+1</f>
         <v>3</v>
@@ -26477,7 +26483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -26549,7 +26555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -26621,7 +26627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -26693,7 +26699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -26765,7 +26771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -26837,7 +26843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -26909,7 +26915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -26981,7 +26987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -27053,7 +27059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" x14ac:dyDescent="0.3">
       <c r="A13" s="15">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -27125,7 +27131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -27197,7 +27203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="A15" s="15">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -27269,7 +27275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -27341,7 +27347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -27413,7 +27419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -27485,7 +27491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -27557,7 +27563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -27629,7 +27635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -27701,7 +27707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -27773,7 +27779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -27845,7 +27851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -27917,7 +27923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -27989,7 +27995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -28061,7 +28067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -28133,7 +28139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -28205,7 +28211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" x14ac:dyDescent="0.3">
       <c r="A29" s="15">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -28277,7 +28283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="A30" s="15">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -28349,7 +28355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="A31" s="15">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -28421,7 +28427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="A32" s="15">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -28493,7 +28499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="A33" s="15">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -28565,7 +28571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" x14ac:dyDescent="0.3">
       <c r="A34" s="15">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -28637,7 +28643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="A35" s="15">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -28709,7 +28715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="A36" s="15">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -28781,7 +28787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="A37" s="15">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -28853,7 +28859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="A38" s="15">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -28925,7 +28931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" x14ac:dyDescent="0.3">
       <c r="A39" s="15">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -28997,7 +29003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="A40" s="15">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -29069,7 +29075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="A41" s="15">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -29141,7 +29147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="A42" s="15">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -29213,7 +29219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="A43" s="15">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -29285,7 +29291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="A44" s="15">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -29357,7 +29363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="A45" s="15">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -29429,7 +29435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="A46" s="15">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -29501,7 +29507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="A47" s="15">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -29573,7 +29579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="A48" s="15">
         <f t="shared" si="1"/>
         <v>47</v>

--- a/Scripts/Prices regionalization.xlsx
+++ b/Scripts/Prices regionalization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Fossil vs. green chemicals\Scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Completed projects\Published\Fossil vs. green chemicals\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562D5297-5F84-427C-B858-9769622F51DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498B700A-3206-4919-857C-D7B49C29D24D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" firstSheet="3" activeTab="12"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8085" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wind LCOH countries" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="US" sheetId="10" r:id="rId12"/>
     <sheet name="PPP" sheetId="11" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -323,7 +323,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -370,133 +370,127 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
-    <border/>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyAlignment="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2888,7 +2882,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
@@ -2906,7 +2900,7 @@
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
-            <a:ext xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11B68518-FE97-4CBC-9A9F-C718C9D42B84}"/>
             </a:ext>
           </a:extLst>
@@ -2929,7 +2923,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
@@ -2947,7 +2941,7 @@
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
-            <a:ext xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6E5868C-D252-44A8-A1A1-3BE678360CAC}"/>
             </a:ext>
           </a:extLst>
@@ -3269,17 +3263,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D726875-4982-4231-B0B7-7E278382FE74}">
   <dimension ref="A1:X20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="12.5546875" bestFit="true" customWidth="true"/>
-    <col min="4" max="4" width="10.88671875" bestFit="true" customWidth="true"/>
-    <col min="7" max="7" width="6.6640625" customWidth="true"/>
-    <col min="10" max="10" width="6.6640625" customWidth="true"/>
-    <col min="11" max="11" width="6.6640625" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B1" s="35">
         <v>2019</v>
       </c>
@@ -3299,7 +3293,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3334,7 +3328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3399,7 +3393,7 @@
         <v>6.4964778242637857</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3464,7 +3458,7 @@
         <v>6.8956619976553917</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -3529,7 +3523,7 @@
         <v>6.9016922742924907</v>
       </c>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3594,7 +3588,7 @@
         <v>5.9491301804454206</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3659,7 +3653,7 @@
         <v>6.5573923196899164</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>64</v>
       </c>
@@ -3724,7 +3718,7 @@
         <v>6.7187500700264966</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -3789,7 +3783,7 @@
         <v>5.1531493311922816</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -3854,7 +3848,7 @@
         <v>6.21069922256887</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12">
         <f>(1-B9/B10)*100</f>
         <v>0</v>
@@ -3868,7 +3862,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M13" s="30" t="s">
         <v>1</v>
       </c>
@@ -3914,7 +3908,7 @@
       </c>
       <c r="X13" s="31"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M14" s="30" t="s">
         <v>2</v>
       </c>
@@ -3960,7 +3954,7 @@
       </c>
       <c r="X14" s="31"/>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M15" s="30" t="s">
         <v>3</v>
       </c>
@@ -4006,7 +4000,7 @@
       </c>
       <c r="X15" s="31"/>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M16" s="30" t="s">
         <v>4</v>
       </c>
@@ -4052,7 +4046,7 @@
       </c>
       <c r="X16" s="31"/>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="13:24" x14ac:dyDescent="0.25">
       <c r="M17" s="30" t="s">
         <v>5</v>
       </c>
@@ -4098,7 +4092,7 @@
       </c>
       <c r="X17" s="31"/>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="13:24" x14ac:dyDescent="0.25">
       <c r="M18" s="30" t="s">
         <v>64</v>
       </c>
@@ -4144,7 +4138,7 @@
       </c>
       <c r="X18" s="31"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="13:24" x14ac:dyDescent="0.25">
       <c r="M19" s="30" t="s">
         <v>6</v>
       </c>
@@ -4190,7 +4184,7 @@
       </c>
       <c r="X19" s="31"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="13:24" x14ac:dyDescent="0.25">
       <c r="N20" s="33">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -4246,15 +4240,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27813F0-E34B-4E1F-AADA-85D890FFA6E1}">
   <dimension ref="A1:Z48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="16"/>
-    <col min="3" max="3" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="4" max="9" width="7.6640625" customWidth="true"/>
-    <col min="10" max="10" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="8.85546875" style="16"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>62</v>
       </c>
@@ -4286,7 +4280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -4348,7 +4342,7 @@
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <f>A2+1</f>
         <v>2</v>
@@ -4411,7 +4405,7 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <f t="shared" ref="A4:A48" si="2">A3+1</f>
         <v>3</v>
@@ -4474,7 +4468,7 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -4537,7 +4531,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -4600,7 +4594,7 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -4663,7 +4657,7 @@
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -4726,7 +4720,7 @@
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -4789,7 +4783,7 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -4852,7 +4846,7 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -4915,7 +4909,7 @@
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -4978,7 +4972,7 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -5041,7 +5035,7 @@
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -5104,7 +5098,7 @@
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -5167,7 +5161,7 @@
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -5230,7 +5224,7 @@
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -5293,7 +5287,7 @@
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -5356,7 +5350,7 @@
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -5419,7 +5413,7 @@
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -5482,7 +5476,7 @@
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -5545,7 +5539,7 @@
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -5608,7 +5602,7 @@
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -5671,7 +5665,7 @@
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -5734,7 +5728,7 @@
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -5797,7 +5791,7 @@
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -5860,7 +5854,7 @@
       <c r="T26" s="8"/>
       <c r="U26" s="8"/>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -5923,7 +5917,7 @@
       <c r="T27" s="8"/>
       <c r="U27" s="8"/>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -5986,7 +5980,7 @@
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -6049,7 +6043,7 @@
       <c r="T29" s="8"/>
       <c r="U29" s="8"/>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -6112,7 +6106,7 @@
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -6175,7 +6169,7 @@
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -6238,7 +6232,7 @@
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -6301,7 +6295,7 @@
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -6364,7 +6358,7 @@
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -6427,7 +6421,7 @@
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -6490,7 +6484,7 @@
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -6553,7 +6547,7 @@
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -6625,7 +6619,7 @@
       <c r="Y38" s="31"/>
       <c r="Z38" s="31"/>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -6688,7 +6682,7 @@
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -6751,7 +6745,7 @@
       <c r="T40" s="8"/>
       <c r="U40" s="8"/>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -6814,7 +6808,7 @@
       <c r="T41" s="8"/>
       <c r="U41" s="8"/>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -6877,7 +6871,7 @@
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -6940,7 +6934,7 @@
       <c r="T43" s="8"/>
       <c r="U43" s="8"/>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <f t="shared" si="2"/>
         <v>43</v>
@@ -7003,7 +6997,7 @@
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <f t="shared" si="2"/>
         <v>44</v>
@@ -7066,7 +7060,7 @@
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -7129,7 +7123,7 @@
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -7192,7 +7186,7 @@
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -7263,15 +7257,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D3FB0C3-01D7-443D-AADC-163D84E338F0}">
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="8.33203125" bestFit="true" customWidth="true"/>
-    <col min="4" max="7" width="7.5546875" bestFit="true" customWidth="true"/>
-    <col min="8" max="8" width="10.88671875" bestFit="true" customWidth="true"/>
-    <col min="9" max="9" width="7.5546875" bestFit="true" customWidth="true"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>62</v>
       </c>
@@ -7300,7 +7294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -7357,7 +7351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <f>A2+1</f>
         <v>2</v>
@@ -7415,7 +7409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <f t="shared" ref="A4:A48" si="2">A3+1</f>
         <v>3</v>
@@ -7473,7 +7467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7531,7 +7525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7589,7 +7583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7647,7 +7641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7705,7 +7699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7763,7 +7757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7821,7 +7815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7879,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7937,7 +7931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -7995,7 +7989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -8053,7 +8047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -8111,7 +8105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -8169,7 +8163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -8227,7 +8221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -8285,7 +8279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -8343,7 +8337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -8401,7 +8395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -8459,7 +8453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -8517,7 +8511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -8575,7 +8569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -8633,7 +8627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -8691,7 +8685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -8749,7 +8743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -8807,7 +8801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -8865,7 +8859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -8923,7 +8917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -8981,7 +8975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -9039,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -9097,7 +9091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -9155,7 +9149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -9213,7 +9207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -9271,7 +9265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -9329,7 +9323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -9387,7 +9381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -9453,7 +9447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -9511,7 +9505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -9569,7 +9563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -9627,7 +9621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -9685,7 +9679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -9743,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <f t="shared" si="2"/>
         <v>43</v>
@@ -9801,7 +9795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <f t="shared" si="2"/>
         <v>44</v>
@@ -9859,7 +9853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -9917,7 +9911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -9975,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -10041,19 +10035,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F34DBA2B-C492-4E14-B9D2-6317C2D70033}">
   <dimension ref="A1:U53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11" bestFit="true" customWidth="true"/>
-    <col min="5" max="5" width="13.5546875" bestFit="true" customWidth="true"/>
-    <col min="6" max="6" width="6.7109375" bestFit="true" customWidth="true"/>
-    <col min="7" max="7" width="7.7109375" bestFit="true" customWidth="true"/>
-    <col min="8" max="8" width="7.7109375" bestFit="true" customWidth="true"/>
-    <col min="9" max="9" width="12.44140625" bestFit="true" customWidth="true"/>
-    <col min="10" max="10" width="13.21875" bestFit="true" customWidth="true"/>
-    <col min="11" max="11" width="13.109375" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>62</v>
       </c>
@@ -10112,7 +10106,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -10172,7 +10166,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f>A2+1</f>
         <v>2</v>
@@ -10233,7 +10227,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <f t="shared" ref="A4:A48" si="1">A3+1</f>
         <v>3</v>
@@ -10294,7 +10288,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -10345,7 +10339,7 @@
       <c r="R5" s="18"/>
       <c r="S5" s="18"/>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -10382,7 +10376,7 @@
         <v>2157.0404745719552</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -10419,7 +10413,7 @@
         <v>2156.2344779048158</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -10456,7 +10450,7 @@
         <v>2156.7595778255131</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -10493,7 +10487,7 @@
         <v>2154.7919082156136</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -10530,7 +10524,7 @@
         <v>2156.6159618651445</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -10567,7 +10561,7 @@
         <v>2154.5191495439794</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -10604,7 +10598,7 @@
         <v>2155.7283031142078</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -10641,7 +10635,7 @@
         <v>2152.8490090770738</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -10678,7 +10672,7 @@
         <v>2140.8894724165611</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -10715,7 +10709,7 @@
         <v>2139.9384576468083</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -10752,7 +10746,7 @@
         <v>2139.0787809409962</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -10789,7 +10783,7 @@
         <v>2139.1509701385235</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -10826,7 +10820,7 @@
         <v>2140.4480416755728</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -10863,7 +10857,7 @@
         <v>2140.1324378104073</v>
       </c>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -10900,7 +10894,7 @@
         <v>2140.7172260215475</v>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -10937,7 +10931,7 @@
         <v>2144.4634149235972</v>
       </c>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -10974,7 +10968,7 @@
         <v>2140.9480116254945</v>
       </c>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -11011,7 +11005,7 @@
         <v>2142.5535090519793</v>
       </c>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -11048,7 +11042,7 @@
         <v>2144.6935076006444</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -11085,7 +11079,7 @@
         <v>2144.0785195481089</v>
       </c>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -11122,7 +11116,7 @@
         <v>2126.3298582536563</v>
       </c>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -11159,7 +11153,7 @@
         <v>2140.777617987741</v>
       </c>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -11196,7 +11190,7 @@
         <v>2122.4745183081895</v>
       </c>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -11233,7 +11227,7 @@
         <v>2122.6422704618403</v>
       </c>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -11270,7 +11264,7 @@
         <v>2126.296494628355</v>
       </c>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -11307,7 +11301,7 @@
         <v>2129.2946504429428</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -11344,7 +11338,7 @@
         <v>2133.6478522332204</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -11381,7 +11375,7 @@
         <v>2135.5688253682638</v>
       </c>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -11418,7 +11412,7 @@
         <v>2142.4788619233004</v>
       </c>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -11455,7 +11449,7 @@
         <v>2144.8311314875759</v>
       </c>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -11492,7 +11486,7 @@
         <v>2140.685898706457</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -11529,7 +11523,7 @@
         <v>2132.43271755863</v>
       </c>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -11566,7 +11560,7 @@
         <v>2493.161468084445</v>
       </c>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -11603,7 +11597,7 @@
         <v>2495.5225230375727</v>
       </c>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -11640,7 +11634,7 @@
         <v>2498.122205172866</v>
       </c>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -11677,7 +11671,7 @@
         <v>2511.2120397095041</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -11714,7 +11708,7 @@
         <v>2524.2025316934823</v>
       </c>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -11751,7 +11745,7 @@
         <v>2522.3170465772955</v>
       </c>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -11788,7 +11782,7 @@
         <v>2519.6986152583786</v>
       </c>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -11825,7 +11819,7 @@
         <v>2529.5085794029592</v>
       </c>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -11862,7 +11856,7 @@
         <v>2520.537885400583</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="17">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -11899,7 +11893,7 @@
         <v>2504.6693147162869</v>
       </c>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="17">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -11936,19 +11930,19 @@
         <v>2503.2367457527521</v>
       </c>
     </row>
-    <row r="49" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C49" s="8"/>
     </row>
-    <row r="50" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C50" s="8"/>
     </row>
-    <row r="51" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C51" s="8"/>
     </row>
-    <row r="52" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C52" s="8"/>
     </row>
-    <row r="53" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C53" s="8"/>
     </row>
   </sheetData>
@@ -11959,15 +11953,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D099D41-EC54-4A9B-8F6F-871BB4D178AD}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="8" width="9.5546875" bestFit="true" customWidth="true"/>
-    <col min="9" max="9" width="11" bestFit="true" customWidth="true"/>
-    <col min="10" max="11" width="9.5546875" bestFit="true" customWidth="true"/>
-    <col min="12" max="12" width="13.33203125" bestFit="true" customWidth="true"/>
+    <col min="2" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>78</v>
       </c>
@@ -12005,7 +11999,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2019</v>
       </c>
@@ -12041,7 +12035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>2020</v>
       </c>
@@ -12076,7 +12070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>2021</v>
       </c>
@@ -12111,7 +12105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>2022</v>
       </c>
@@ -12146,7 +12140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>78</v>
       </c>
@@ -12184,7 +12178,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>2019</v>
       </c>
@@ -12219,7 +12213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>2020</v>
       </c>
@@ -12254,7 +12248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>2021</v>
       </c>
@@ -12289,7 +12283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>2022</v>
       </c>
@@ -12324,7 +12318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -12337,7 +12331,7 @@
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>79</v>
       </c>
@@ -12375,7 +12369,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>2019</v>
       </c>
@@ -12420,7 +12414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>2020</v>
       </c>
@@ -12465,7 +12459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>2021</v>
       </c>
@@ -12510,7 +12504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>2022</v>
       </c>
@@ -12563,16 +12557,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871DB5C8-AD7B-4707-A20F-1A3E279300AB}">
   <dimension ref="A1:V27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="12.5546875" bestFit="true" customWidth="true"/>
-    <col min="4" max="4" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="7" max="7" width="7.6640625" customWidth="true"/>
-    <col min="10" max="11" width="7.6640625" customWidth="true"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" customWidth="1"/>
+    <col min="10" max="11" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B1" s="35">
         <v>2019</v>
       </c>
@@ -12592,7 +12586,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -12627,7 +12621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -12662,7 +12656,7 @@
         <v>10.530004206601616</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
@@ -12697,7 +12691,7 @@
         <v>9.7107722150761919</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -12741,7 +12735,7 @@
       <c r="U5" s="13"/>
       <c r="V5" s="13"/>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>64</v>
       </c>
@@ -12785,7 +12779,7 @@
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
@@ -12829,7 +12823,7 @@
       <c r="U7" s="13"/>
       <c r="V7" s="13"/>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>63</v>
       </c>
@@ -12873,7 +12867,7 @@
       <c r="U8" s="13"/>
       <c r="V8" s="13"/>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
@@ -12917,7 +12911,7 @@
       <c r="U9" s="13"/>
       <c r="V9" s="13"/>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C10" s="10"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
@@ -12929,7 +12923,7 @@
       <c r="U10" s="13"/>
       <c r="V10" s="13"/>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B11">
         <f>(1-B7/B9)*100</f>
         <v>16.029411764705891</v>
@@ -12952,7 +12946,7 @@
       <c r="U11" s="13"/>
       <c r="V11" s="13"/>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
@@ -12963,7 +12957,7 @@
       <c r="U12" s="13"/>
       <c r="V12" s="13"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="4"/>
       <c r="C13" s="12"/>
@@ -12985,7 +12979,7 @@
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="4"/>
       <c r="C14" s="12"/>
@@ -13007,7 +13001,7 @@
       <c r="U14" s="13"/>
       <c r="V14" s="13"/>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="12"/>
@@ -13029,7 +13023,7 @@
       <c r="U15" s="13"/>
       <c r="V15" s="13"/>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
@@ -13040,7 +13034,7 @@
       <c r="U16" s="13"/>
       <c r="V16" s="13"/>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
@@ -13051,7 +13045,7 @@
       <c r="U17" s="13"/>
       <c r="V17" s="13"/>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
@@ -13062,7 +13056,7 @@
       <c r="U18" s="13"/>
       <c r="V18" s="13"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
@@ -13073,7 +13067,7 @@
       <c r="U19" s="13"/>
       <c r="V19" s="13"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
@@ -13084,7 +13078,7 @@
       <c r="U20" s="13"/>
       <c r="V20" s="13"/>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
@@ -13095,7 +13089,7 @@
       <c r="U21" s="13"/>
       <c r="V21" s="13"/>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -13106,7 +13100,7 @@
       <c r="U22" s="13"/>
       <c r="V22" s="13"/>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
@@ -13117,7 +13111,7 @@
       <c r="U23" s="13"/>
       <c r="V23" s="13"/>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
@@ -13128,7 +13122,7 @@
       <c r="U24" s="13"/>
       <c r="V24" s="13"/>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N25" s="13"/>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
@@ -13139,7 +13133,7 @@
       <c r="U25" s="13"/>
       <c r="V25" s="13"/>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N26" s="13"/>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
@@ -13150,7 +13144,7 @@
       <c r="U26" s="13"/>
       <c r="V26" s="13"/>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="14:22" x14ac:dyDescent="0.25">
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
@@ -13174,14 +13168,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B9B229-C3D6-4135-8FAF-20ADF246D35B}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="true" customWidth="true"/>
-    <col min="2" max="9" width="6.6640625" bestFit="true" customWidth="true"/>
-    <col min="10" max="10" width="14.109375" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>9</v>
       </c>
@@ -13219,7 +13213,7 @@
       <c r="Q1" s="22"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>47</v>
       </c>
@@ -13251,7 +13245,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>48</v>
       </c>
@@ -13281,7 +13275,7 @@
       </c>
       <c r="J3" s="39"/>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>49</v>
       </c>
@@ -13311,7 +13305,7 @@
       </c>
       <c r="J4" s="39"/>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>50</v>
       </c>
@@ -13341,7 +13335,7 @@
       </c>
       <c r="J5" s="39"/>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>51</v>
       </c>
@@ -13371,7 +13365,7 @@
       </c>
       <c r="J6" s="39"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>52</v>
       </c>
@@ -13401,7 +13395,7 @@
       </c>
       <c r="J7" s="39"/>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>53</v>
       </c>
@@ -13431,7 +13425,7 @@
       </c>
       <c r="J8" s="39"/>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>54</v>
       </c>
@@ -13461,7 +13455,7 @@
       </c>
       <c r="J9" s="39"/>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>55</v>
       </c>
@@ -13491,7 +13485,7 @@
       </c>
       <c r="J10" s="39"/>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>56</v>
       </c>
@@ -13521,7 +13515,7 @@
       </c>
       <c r="J11" s="39"/>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
@@ -13551,7 +13545,7 @@
       </c>
       <c r="J12" s="40"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>47</v>
       </c>
@@ -13583,7 +13577,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>48</v>
       </c>
@@ -13613,7 +13607,7 @@
       </c>
       <c r="J14" s="39"/>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>49</v>
       </c>
@@ -13643,7 +13637,7 @@
       </c>
       <c r="J15" s="39"/>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>50</v>
       </c>
@@ -13673,7 +13667,7 @@
       </c>
       <c r="J16" s="39"/>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>51</v>
       </c>
@@ -13703,7 +13697,7 @@
       </c>
       <c r="J17" s="39"/>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>52</v>
       </c>
@@ -13733,7 +13727,7 @@
       </c>
       <c r="J18" s="39"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>53</v>
       </c>
@@ -13763,7 +13757,7 @@
       </c>
       <c r="J19" s="39"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>54</v>
       </c>
@@ -13793,7 +13787,7 @@
       </c>
       <c r="J20" s="39"/>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>55</v>
       </c>
@@ -13823,7 +13817,7 @@
       </c>
       <c r="J21" s="39"/>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>56</v>
       </c>
@@ -13853,7 +13847,7 @@
       </c>
       <c r="J22" s="39"/>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
         <v>57</v>
       </c>
@@ -13883,7 +13877,7 @@
       </c>
       <c r="J23" s="40"/>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>47</v>
       </c>
@@ -13915,7 +13909,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>48</v>
       </c>
@@ -13945,7 +13939,7 @@
       </c>
       <c r="J25" s="37"/>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>49</v>
       </c>
@@ -13975,7 +13969,7 @@
       </c>
       <c r="J26" s="37"/>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
         <v>50</v>
       </c>
@@ -14005,7 +13999,7 @@
       </c>
       <c r="J27" s="37"/>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>51</v>
       </c>
@@ -14035,7 +14029,7 @@
       </c>
       <c r="J28" s="37"/>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>52</v>
       </c>
@@ -14065,7 +14059,7 @@
       </c>
       <c r="J29" s="37"/>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>53</v>
       </c>
@@ -14095,7 +14089,7 @@
       </c>
       <c r="J30" s="37"/>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>54</v>
       </c>
@@ -14125,7 +14119,7 @@
       </c>
       <c r="J31" s="37"/>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>55</v>
       </c>
@@ -14155,7 +14149,7 @@
       </c>
       <c r="J32" s="37"/>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>56</v>
       </c>
@@ -14185,7 +14179,7 @@
       </c>
       <c r="J33" s="37"/>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
         <v>57</v>
       </c>
@@ -14229,19 +14223,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF35DFB-0E09-4689-BF8E-0ABADEA145F5}">
   <dimension ref="A1:AG40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="7.6640625" customWidth="true"/>
-    <col min="3" max="4" width="6.6640625" customWidth="true"/>
-    <col min="5" max="5" width="7.6640625" customWidth="true"/>
-    <col min="6" max="6" width="6.6640625" customWidth="true"/>
-    <col min="7" max="7" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="8" max="8" width="6.6640625" customWidth="true"/>
-    <col min="9" max="9" width="14.109375" customWidth="true"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>9</v>
       </c>
@@ -14268,7 +14262,7 @@
       </c>
       <c r="I1" s="29"/>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>47</v>
       </c>
@@ -14304,7 +14298,7 @@
       <c r="O2" s="22"/>
       <c r="P2" s="22"/>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>48</v>
       </c>
@@ -14331,7 +14325,7 @@
       </c>
       <c r="I3" s="39"/>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>49</v>
       </c>
@@ -14367,7 +14361,7 @@
       <c r="AF4" s="22"/>
       <c r="AG4" s="22"/>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>50</v>
       </c>
@@ -14403,7 +14397,7 @@
       <c r="AF5" s="22"/>
       <c r="AG5" s="22"/>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>51</v>
       </c>
@@ -14439,7 +14433,7 @@
       <c r="AF6" s="22"/>
       <c r="AG6" s="22"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>52</v>
       </c>
@@ -14466,7 +14460,7 @@
       </c>
       <c r="I7" s="39"/>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>53</v>
       </c>
@@ -14493,7 +14487,7 @@
       </c>
       <c r="I8" s="39"/>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>54</v>
       </c>
@@ -14520,7 +14514,7 @@
       </c>
       <c r="I9" s="39"/>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>55</v>
       </c>
@@ -14547,7 +14541,7 @@
       </c>
       <c r="I10" s="39"/>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>56</v>
       </c>
@@ -14574,7 +14568,7 @@
       </c>
       <c r="I11" s="39"/>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
@@ -14601,7 +14595,7 @@
       </c>
       <c r="I12" s="40"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>47</v>
       </c>
@@ -14637,7 +14631,7 @@
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>48</v>
       </c>
@@ -14664,7 +14658,7 @@
       </c>
       <c r="I14" s="39"/>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>49</v>
       </c>
@@ -14691,7 +14685,7 @@
       </c>
       <c r="I15" s="39"/>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>50</v>
       </c>
@@ -14718,7 +14712,7 @@
       </c>
       <c r="I16" s="39"/>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>51</v>
       </c>
@@ -14745,7 +14739,7 @@
       </c>
       <c r="I17" s="39"/>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>52</v>
       </c>
@@ -14772,7 +14766,7 @@
       </c>
       <c r="I18" s="39"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>53</v>
       </c>
@@ -14799,7 +14793,7 @@
       </c>
       <c r="I19" s="39"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>54</v>
       </c>
@@ -14826,7 +14820,7 @@
       </c>
       <c r="I20" s="39"/>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>55</v>
       </c>
@@ -14853,7 +14847,7 @@
       </c>
       <c r="I21" s="39"/>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>56</v>
       </c>
@@ -14880,7 +14874,7 @@
       </c>
       <c r="I22" s="39"/>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
         <v>57</v>
       </c>
@@ -14907,7 +14901,7 @@
       </c>
       <c r="I23" s="40"/>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>47</v>
       </c>
@@ -14943,7 +14937,7 @@
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>48</v>
       </c>
@@ -14970,7 +14964,7 @@
       </c>
       <c r="I25" s="37"/>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>49</v>
       </c>
@@ -14997,7 +14991,7 @@
       </c>
       <c r="I26" s="37"/>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
         <v>50</v>
       </c>
@@ -15024,7 +15018,7 @@
       </c>
       <c r="I27" s="37"/>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>51</v>
       </c>
@@ -15052,7 +15046,7 @@
       <c r="I28" s="37"/>
       <c r="J28" s="21"/>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>52</v>
       </c>
@@ -15083,7 +15077,7 @@
       <c r="L29" s="21"/>
       <c r="M29" s="21"/>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>53</v>
       </c>
@@ -15111,7 +15105,7 @@
       <c r="I30" s="37"/>
       <c r="J30" s="21"/>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>54</v>
       </c>
@@ -15139,7 +15133,7 @@
       <c r="I31" s="37"/>
       <c r="J31" s="21"/>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>55</v>
       </c>
@@ -15167,7 +15161,7 @@
       <c r="I32" s="37"/>
       <c r="J32" s="21"/>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>56</v>
       </c>
@@ -15195,7 +15189,7 @@
       <c r="I33" s="37"/>
       <c r="J33" s="21"/>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
         <v>57</v>
       </c>
@@ -15223,7 +15217,7 @@
       <c r="I34" s="38"/>
       <c r="J34" s="21"/>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
       <c r="G35" s="21"/>
@@ -15231,7 +15225,7 @@
       <c r="I35" s="21"/>
       <c r="J35" s="21"/>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21"/>
@@ -15239,7 +15233,7 @@
       <c r="I36" s="21"/>
       <c r="J36" s="21"/>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
@@ -15247,13 +15241,13 @@
       <c r="I37" s="21"/>
       <c r="J37" s="21"/>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E38" s="21"/>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E39" s="21"/>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -15270,14 +15264,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82DCA3AB-7AE8-4026-8261-B5E7C73AC0DA}">
   <dimension ref="A1:J48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="true" customWidth="true"/>
-    <col min="2" max="3" width="8.33203125" bestFit="true" customWidth="true"/>
-    <col min="9" max="9" width="10.88671875" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -15309,7 +15303,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -15342,7 +15336,7 @@
         <v>49.41</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -15375,7 +15369,7 @@
         <v>42.81</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -15408,7 +15402,7 @@
         <v>30.61</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -15441,7 +15435,7 @@
         <v>36.97</v>
       </c>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -15474,7 +15468,7 @@
         <v>37.83</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -15507,7 +15501,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
@@ -15540,7 +15534,7 @@
         <v>39.71</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
@@ -15573,7 +15567,7 @@
         <v>36.82</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>19</v>
       </c>
@@ -15606,7 +15600,7 @@
         <v>35.770000000000003</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -15639,7 +15633,7 @@
         <v>36.950000000000003</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>21</v>
       </c>
@@ -15672,7 +15666,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>22</v>
       </c>
@@ -15705,7 +15699,7 @@
         <v>31.97</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -15738,7 +15732,7 @@
         <v>34.979999999999997</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
@@ -15771,7 +15765,7 @@
         <v>21.91</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
@@ -15804,7 +15798,7 @@
         <v>22.52</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
@@ -15837,7 +15831,7 @@
         <v>17.05</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
@@ -15870,7 +15864,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
@@ -15903,7 +15897,7 @@
         <v>26.23</v>
       </c>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -15936,7 +15930,7 @@
         <v>30.07</v>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
@@ -15969,7 +15963,7 @@
         <v>34.89</v>
       </c>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>31</v>
       </c>
@@ -16002,7 +15996,7 @@
         <v>43.68</v>
       </c>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>32</v>
       </c>
@@ -16035,7 +16029,7 @@
         <v>33.96</v>
       </c>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>33</v>
       </c>
@@ -16068,7 +16062,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>34</v>
       </c>
@@ -16101,7 +16095,7 @@
         <v>43.55</v>
       </c>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>35</v>
       </c>
@@ -16134,7 +16128,7 @@
         <v>52.79</v>
       </c>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>36</v>
       </c>
@@ -16167,7 +16161,7 @@
         <v>48.71</v>
       </c>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
@@ -16200,7 +16194,7 @@
         <v>47.18</v>
       </c>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
@@ -16233,7 +16227,7 @@
         <v>53.66</v>
       </c>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
@@ -16266,7 +16260,7 @@
         <v>53.33</v>
       </c>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
@@ -16299,7 +16293,7 @@
         <v>74.13</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
@@ -16332,7 +16326,7 @@
         <v>81.290000000000006</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
@@ -16365,7 +16359,7 @@
         <v>82.81</v>
       </c>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
@@ -16398,7 +16392,7 @@
         <v>128.34</v>
       </c>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>44</v>
       </c>
@@ -16431,7 +16425,7 @@
         <v>139.54</v>
       </c>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>45</v>
       </c>
@@ -16464,7 +16458,7 @@
         <v>176.25</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>46</v>
       </c>
@@ -16497,7 +16491,7 @@
         <v>220.96</v>
       </c>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>47</v>
       </c>
@@ -16530,7 +16524,7 @@
         <v>167.87</v>
       </c>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>48</v>
       </c>
@@ -16563,7 +16557,7 @@
         <v>128.78</v>
       </c>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>49</v>
       </c>
@@ -16596,7 +16590,7 @@
         <v>251.76</v>
       </c>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>50</v>
       </c>
@@ -16629,7 +16623,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>51</v>
       </c>
@@ -16662,7 +16656,7 @@
         <v>177.51</v>
       </c>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>52</v>
       </c>
@@ -16695,7 +16689,7 @@
         <v>218.18</v>
       </c>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>53</v>
       </c>
@@ -16728,7 +16722,7 @@
         <v>315.26</v>
       </c>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>54</v>
       </c>
@@ -16761,7 +16755,7 @@
         <v>469.35</v>
       </c>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>55</v>
       </c>
@@ -16794,7 +16788,7 @@
         <v>360.18</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>56</v>
       </c>
@@ -16827,7 +16821,7 @@
         <v>157.78</v>
       </c>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>57</v>
       </c>
@@ -16868,16 +16862,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1672A6CF-CF66-476C-9F50-013698E5ECE7}">
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="10"/>
-    <col min="3" max="9" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="10" max="10" width="10.88671875" bestFit="true" customWidth="true"/>
-    <col min="11" max="11" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="12" max="50" width="11.6640625" customWidth="true"/>
+    <col min="1" max="1" width="8.85546875" style="10"/>
+    <col min="3" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="50" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
@@ -16912,7 +16906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -16984,7 +16978,7 @@
       </c>
       <c r="V2" s="8"/>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <f>A2+1</f>
         <v>2</v>
@@ -17057,7 +17051,7 @@
       </c>
       <c r="V3" s="8"/>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <f t="shared" ref="A4:A48" si="10">A3+1</f>
         <v>3</v>
@@ -17130,7 +17124,7 @@
       </c>
       <c r="V4" s="8"/>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f t="shared" si="10"/>
         <v>4</v>
@@ -17203,7 +17197,7 @@
       </c>
       <c r="V5" s="8"/>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <f t="shared" si="10"/>
         <v>5</v>
@@ -17276,7 +17270,7 @@
       </c>
       <c r="V6" s="8"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <f t="shared" si="10"/>
         <v>6</v>
@@ -17349,7 +17343,7 @@
       </c>
       <c r="V7" s="8"/>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <f t="shared" si="10"/>
         <v>7</v>
@@ -17422,7 +17416,7 @@
       </c>
       <c r="V8" s="8"/>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <f t="shared" si="10"/>
         <v>8</v>
@@ -17495,7 +17489,7 @@
       </c>
       <c r="V9" s="8"/>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <f t="shared" si="10"/>
         <v>9</v>
@@ -17568,7 +17562,7 @@
       </c>
       <c r="V10" s="8"/>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <f t="shared" si="10"/>
         <v>10</v>
@@ -17641,7 +17635,7 @@
       </c>
       <c r="V11" s="8"/>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <f t="shared" si="10"/>
         <v>11</v>
@@ -17714,7 +17708,7 @@
       </c>
       <c r="V12" s="8"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <f t="shared" si="10"/>
         <v>12</v>
@@ -17787,7 +17781,7 @@
       </c>
       <c r="V13" s="8"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <f t="shared" si="10"/>
         <v>13</v>
@@ -17860,7 +17854,7 @@
       </c>
       <c r="V14" s="8"/>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <f t="shared" si="10"/>
         <v>14</v>
@@ -17933,7 +17927,7 @@
       </c>
       <c r="V15" s="8"/>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <f t="shared" si="10"/>
         <v>15</v>
@@ -18006,7 +18000,7 @@
       </c>
       <c r="V16" s="8"/>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -18079,7 +18073,7 @@
       </c>
       <c r="V17" s="8"/>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="10"/>
         <v>17</v>
@@ -18152,7 +18146,7 @@
       </c>
       <c r="V18" s="8"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <f t="shared" si="10"/>
         <v>18</v>
@@ -18225,7 +18219,7 @@
       </c>
       <c r="V19" s="8"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <f t="shared" si="10"/>
         <v>19</v>
@@ -18298,7 +18292,7 @@
       </c>
       <c r="V20" s="8"/>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <f t="shared" si="10"/>
         <v>20</v>
@@ -18371,7 +18365,7 @@
       </c>
       <c r="V21" s="8"/>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <f t="shared" si="10"/>
         <v>21</v>
@@ -18444,7 +18438,7 @@
       </c>
       <c r="V22" s="8"/>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <f t="shared" si="10"/>
         <v>22</v>
@@ -18517,7 +18511,7 @@
       </c>
       <c r="V23" s="8"/>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <f t="shared" si="10"/>
         <v>23</v>
@@ -18590,7 +18584,7 @@
       </c>
       <c r="V24" s="8"/>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -18663,7 +18657,7 @@
       </c>
       <c r="V25" s="8"/>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -18736,7 +18730,7 @@
       </c>
       <c r="V26" s="8"/>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -18809,7 +18803,7 @@
       </c>
       <c r="V27" s="8"/>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -18882,7 +18876,7 @@
       </c>
       <c r="V28" s="8"/>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -18955,7 +18949,7 @@
       </c>
       <c r="V29" s="8"/>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -19028,7 +19022,7 @@
       </c>
       <c r="V30" s="8"/>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -19101,7 +19095,7 @@
       </c>
       <c r="V31" s="8"/>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -19174,7 +19168,7 @@
       </c>
       <c r="V32" s="8"/>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -19247,7 +19241,7 @@
       </c>
       <c r="V33" s="8"/>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -19320,7 +19314,7 @@
       </c>
       <c r="V34" s="8"/>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -19393,7 +19387,7 @@
       </c>
       <c r="V35" s="8"/>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -19466,7 +19460,7 @@
       </c>
       <c r="V36" s="8"/>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -19539,7 +19533,7 @@
       </c>
       <c r="V37" s="8"/>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -19612,7 +19606,7 @@
       </c>
       <c r="V38" s="8"/>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -19685,7 +19679,7 @@
       </c>
       <c r="V39" s="8"/>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -19758,7 +19752,7 @@
       </c>
       <c r="V40" s="8"/>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -19831,7 +19825,7 @@
       </c>
       <c r="V41" s="8"/>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -19904,7 +19898,7 @@
       </c>
       <c r="V42" s="8"/>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -19977,7 +19971,7 @@
       </c>
       <c r="V43" s="8"/>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -20050,7 +20044,7 @@
       </c>
       <c r="V44" s="8"/>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -20123,7 +20117,7 @@
       </c>
       <c r="V45" s="8"/>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -20196,7 +20190,7 @@
       </c>
       <c r="V46" s="8"/>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <f t="shared" si="10"/>
         <v>46</v>
@@ -20269,7 +20263,7 @@
       </c>
       <c r="V47" s="8"/>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -20351,15 +20345,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAED7290-7707-45C0-BC3F-97D9971BFCE3}">
   <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="10"/>
-    <col min="3" max="3" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="4" max="9" width="7.6640625" customWidth="true"/>
-    <col min="10" max="10" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="8.85546875" style="10"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
@@ -20391,7 +20385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -20455,7 +20449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <f>A2+1</f>
         <v>2</v>
@@ -20520,7 +20514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <f t="shared" ref="A4:A48" si="9">A3+1</f>
         <v>3</v>
@@ -20585,7 +20579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f t="shared" si="9"/>
         <v>4</v>
@@ -20650,7 +20644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <f t="shared" si="9"/>
         <v>5</v>
@@ -20715,7 +20709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <f t="shared" si="9"/>
         <v>6</v>
@@ -20780,7 +20774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <f t="shared" si="9"/>
         <v>7</v>
@@ -20845,7 +20839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <f t="shared" si="9"/>
         <v>8</v>
@@ -20910,7 +20904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <f t="shared" si="9"/>
         <v>9</v>
@@ -20975,7 +20969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <f t="shared" si="9"/>
         <v>10</v>
@@ -21040,7 +21034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <f t="shared" si="9"/>
         <v>11</v>
@@ -21105,7 +21099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <f t="shared" si="9"/>
         <v>12</v>
@@ -21170,7 +21164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
@@ -21235,7 +21229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
@@ -21300,7 +21294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <f t="shared" si="9"/>
         <v>15</v>
@@ -21365,7 +21359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="9"/>
         <v>16</v>
@@ -21430,7 +21424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="9"/>
         <v>17</v>
@@ -21495,7 +21489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <f t="shared" si="9"/>
         <v>18</v>
@@ -21560,7 +21554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <f t="shared" si="9"/>
         <v>19</v>
@@ -21625,7 +21619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <f t="shared" si="9"/>
         <v>20</v>
@@ -21690,7 +21684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <f t="shared" si="9"/>
         <v>21</v>
@@ -21755,7 +21749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <f t="shared" si="9"/>
         <v>22</v>
@@ -21820,7 +21814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <f t="shared" si="9"/>
         <v>23</v>
@@ -21885,7 +21879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -21950,7 +21944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -22015,7 +22009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -22080,7 +22074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -22145,7 +22139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -22210,7 +22204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -22275,7 +22269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -22340,7 +22334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -22405,7 +22399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -22470,7 +22464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -22535,7 +22529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -22600,7 +22594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <f t="shared" si="9"/>
         <v>35</v>
@@ -22665,7 +22659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -22730,7 +22724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -22796,7 +22790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -22861,7 +22855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -22926,7 +22920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -22991,7 +22985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -23056,7 +23050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -23121,7 +23115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -23186,7 +23180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -23251,7 +23245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <f t="shared" si="9"/>
         <v>45</v>
@@ -23316,7 +23310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <f t="shared" si="9"/>
         <v>46</v>
@@ -23381,7 +23375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -23454,12 +23448,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9409F663-E7D0-44EE-A820-32D1CD0043C0}">
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="9" width="7.6640625" bestFit="true" customWidth="true"/>
+    <col min="3" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
@@ -23488,7 +23482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -23545,7 +23539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <f>A2+1</f>
         <v>2</v>
@@ -23603,7 +23597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <f t="shared" ref="A4:A48" si="8">A3+1</f>
         <v>3</v>
@@ -23661,7 +23655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f t="shared" si="8"/>
         <v>4</v>
@@ -23719,7 +23713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -23777,7 +23771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -23835,7 +23829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <f t="shared" si="8"/>
         <v>7</v>
@@ -23893,7 +23887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f t="shared" si="8"/>
         <v>8</v>
@@ -23951,7 +23945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <f t="shared" si="8"/>
         <v>9</v>
@@ -24009,7 +24003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f t="shared" si="8"/>
         <v>10</v>
@@ -24067,7 +24061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -24125,7 +24119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f t="shared" si="8"/>
         <v>12</v>
@@ -24183,7 +24177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <f t="shared" si="8"/>
         <v>13</v>
@@ -24241,7 +24235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -24299,7 +24293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <f t="shared" si="8"/>
         <v>15</v>
@@ -24357,7 +24351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f t="shared" si="8"/>
         <v>16</v>
@@ -24415,7 +24409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <f t="shared" si="8"/>
         <v>17</v>
@@ -24473,7 +24467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <f t="shared" si="8"/>
         <v>18</v>
@@ -24531,7 +24525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <f t="shared" si="8"/>
         <v>19</v>
@@ -24589,7 +24583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <f t="shared" si="8"/>
         <v>20</v>
@@ -24647,7 +24641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <f t="shared" si="8"/>
         <v>21</v>
@@ -24705,7 +24699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <f t="shared" si="8"/>
         <v>22</v>
@@ -24763,7 +24757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <f t="shared" si="8"/>
         <v>23</v>
@@ -24821,7 +24815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <f t="shared" si="8"/>
         <v>24</v>
@@ -24879,7 +24873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <f t="shared" si="8"/>
         <v>25</v>
@@ -24937,7 +24931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <f t="shared" si="8"/>
         <v>26</v>
@@ -24995,7 +24989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -25053,7 +25047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -25111,7 +25105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -25169,7 +25163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -25227,7 +25221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <f t="shared" si="8"/>
         <v>31</v>
@@ -25285,7 +25279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -25343,7 +25337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <f t="shared" si="8"/>
         <v>33</v>
@@ -25401,7 +25395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <f t="shared" si="8"/>
         <v>34</v>
@@ -25459,7 +25453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <f t="shared" si="8"/>
         <v>35</v>
@@ -25517,7 +25511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <f t="shared" si="8"/>
         <v>36</v>
@@ -25575,7 +25569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <f t="shared" si="8"/>
         <v>37</v>
@@ -25635,7 +25629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <f t="shared" si="8"/>
         <v>38</v>
@@ -25693,7 +25687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <f t="shared" si="8"/>
         <v>39</v>
@@ -25751,7 +25745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <f t="shared" si="8"/>
         <v>40</v>
@@ -25809,7 +25803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -25867,7 +25861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -25925,7 +25919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -25983,7 +25977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -26041,7 +26035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -26099,7 +26093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -26157,7 +26151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -26223,17 +26217,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A376DB6-4E6C-48EF-8A7B-FCA6DAFAE291}">
   <dimension ref="A1:U48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="15"/>
-    <col min="3" max="8" width="7.6640625" customWidth="true"/>
-    <col min="9" max="9" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="10" max="10" width="10.88671875" bestFit="true" customWidth="true"/>
-    <col min="11" max="11" width="7.6640625" bestFit="true" customWidth="true"/>
-    <col min="12" max="50" width="11.6640625" customWidth="true"/>
+    <col min="1" max="1" width="8.85546875" style="15"/>
+    <col min="3" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="50" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>62</v>
       </c>
@@ -26268,7 +26262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -26339,7 +26333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
         <f>A2+1</f>
         <v>2</v>
@@ -26411,7 +26405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <f t="shared" ref="A4:A48" si="1">A3+1</f>
         <v>3</v>
@@ -26483,7 +26477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -26555,7 +26549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -26627,7 +26621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -26699,7 +26693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -26771,7 +26765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -26843,7 +26837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -26915,7 +26909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -26987,7 +26981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -27059,7 +27053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -27131,7 +27125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -27203,7 +27197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -27275,7 +27269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -27347,7 +27341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -27419,7 +27413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -27491,7 +27485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -27563,7 +27557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -27635,7 +27629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -27707,7 +27701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -27779,7 +27773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -27851,7 +27845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -27923,7 +27917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -27995,7 +27989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -28067,7 +28061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -28139,7 +28133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -28211,7 +28205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -28283,7 +28277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -28355,7 +28349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -28427,7 +28421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -28499,7 +28493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -28571,7 +28565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -28643,7 +28637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -28715,7 +28709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -28787,7 +28781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -28859,7 +28853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -28931,7 +28925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -29003,7 +28997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -29075,7 +29069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -29147,7 +29141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -29219,7 +29213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -29291,7 +29285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -29363,7 +29357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -29435,7 +29429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -29507,7 +29501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -29579,7 +29573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="15">
         <f t="shared" si="1"/>
         <v>47</v>
